--- a/build/Profitly.xlsx
+++ b/build/Profitly.xlsx
@@ -428,14 +428,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F0FC"/>
-        <bgColor rgb="00F3F0FC"/>
+        <fgColor rgb="00F0F1F3"/>
+        <bgColor rgb="00F0F1F3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F0F1F3"/>
-        <bgColor rgb="00F0F1F3"/>
+        <fgColor rgb="00F3F0FC"/>
+        <bgColor rgb="00F3F0FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -587,7 +587,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -663,7 +663,7 @@
     <xf numFmtId="165" fontId="17" fillId="4" borderId="5" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -723,14 +723,6 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="7" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
     <xf numFmtId="167" fontId="12" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
@@ -747,7 +739,7 @@
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -762,15 +754,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="7" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="1" fillId="8" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="7" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -2097,12 +2089,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="70" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="68" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
@@ -2186,32 +2178,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="70" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>Lst_Categorias</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="68" t="inlineStr">
         <is>
           <t>Lst_Canales</t>
         </is>
       </c>
-      <c r="C1" s="70" t="inlineStr">
+      <c r="C1" s="68" t="inlineStr">
         <is>
           <t>Lst_CategoriasGasto</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="68" t="inlineStr">
         <is>
           <t>Lst_TiposGasto</t>
         </is>
       </c>
-      <c r="E1" s="70" t="inlineStr">
+      <c r="E1" s="68" t="inlineStr">
         <is>
           <t>Lst_Monedas</t>
         </is>
       </c>
-      <c r="F1" s="70" t="inlineStr">
+      <c r="F1" s="68" t="inlineStr">
         <is>
           <t>Lst_PeriodosRapidos</t>
         </is>
@@ -2701,11 +2693,11 @@
         <f>IF(Dash_Granularidad="Mensual",TEXT(EDATE(TODAY(),-5),"MMM"),"Sem. "&amp;TEXT(TODAY()-5*7,"DD/MM"))</f>
         <v/>
       </c>
-      <c r="B23" s="71">
+      <c r="B23" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-5-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-5)),SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-5*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-5*7))</f>
         <v/>
       </c>
-      <c r="C23" s="71">
+      <c r="C23" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-5-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-5)),SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-5*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-5*7))</f>
         <v/>
       </c>
@@ -2715,11 +2707,11 @@
         <f>IF(Dash_Granularidad="Mensual",TEXT(EDATE(TODAY(),-4),"MMM"),"Sem. "&amp;TEXT(TODAY()-4*7,"DD/MM"))</f>
         <v/>
       </c>
-      <c r="B24" s="71">
+      <c r="B24" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-4-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-4)),SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-4*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-4*7))</f>
         <v/>
       </c>
-      <c r="C24" s="71">
+      <c r="C24" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-4-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-4)),SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-4*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-4*7))</f>
         <v/>
       </c>
@@ -2729,11 +2721,11 @@
         <f>IF(Dash_Granularidad="Mensual",TEXT(EDATE(TODAY(),-3),"MMM"),"Sem. "&amp;TEXT(TODAY()-3*7,"DD/MM"))</f>
         <v/>
       </c>
-      <c r="B25" s="71">
+      <c r="B25" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-3-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-3)),SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-3*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-3*7))</f>
         <v/>
       </c>
-      <c r="C25" s="71">
+      <c r="C25" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-3-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-3)),SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-3*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-3*7))</f>
         <v/>
       </c>
@@ -2743,11 +2735,11 @@
         <f>IF(Dash_Granularidad="Mensual",TEXT(EDATE(TODAY(),-2),"MMM"),"Sem. "&amp;TEXT(TODAY()-2*7,"DD/MM"))</f>
         <v/>
       </c>
-      <c r="B26" s="71">
+      <c r="B26" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-2-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-2)),SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-2*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-2*7))</f>
         <v/>
       </c>
-      <c r="C26" s="71">
+      <c r="C26" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-2-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-2)),SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-2*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-2*7))</f>
         <v/>
       </c>
@@ -2757,11 +2749,11 @@
         <f>IF(Dash_Granularidad="Mensual",TEXT(EDATE(TODAY(),-1),"MMM"),"Sem. "&amp;TEXT(TODAY()-1*7,"DD/MM"))</f>
         <v/>
       </c>
-      <c r="B27" s="71">
+      <c r="B27" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-1-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-1)),SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-1*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-1*7))</f>
         <v/>
       </c>
-      <c r="C27" s="71">
+      <c r="C27" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-1-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-1)),SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-1*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-1*7))</f>
         <v/>
       </c>
@@ -2771,11 +2763,11 @@
         <f>IF(Dash_Granularidad="Mensual",TEXT(EDATE(TODAY(),-0),"MMM"),"Sem. "&amp;TEXT(TODAY()-0*7,"DD/MM"))</f>
         <v/>
       </c>
-      <c r="B28" s="71">
+      <c r="B28" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-0-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-0)),SUMIFS(tbl_Ventas[Venta total],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-0*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-0*7))</f>
         <v/>
       </c>
-      <c r="C28" s="71">
+      <c r="C28" s="69">
         <f>IF(Dash_Granularidad="Mensual",SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;EOMONTH(TODAY(),-0-1)+1,tbl_Ventas[Fecha],"&lt;="&amp;EOMONTH(TODAY(),-0)),SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],"&gt;="&amp;TODAY()-0*7-6,tbl_Ventas[Fecha],"&lt;="&amp;TODAY()-0*7))</f>
         <v/>
       </c>
@@ -2804,7 +2796,7 @@
         <f>IFERROR(INDEX(tbl_Productos[Producto],MATCH(B33,tbl_Productos[Ganancia total],0)),"")</f>
         <v/>
       </c>
-      <c r="B33" s="71">
+      <c r="B33" s="69">
         <f>IFERROR(LARGE(tbl_Productos[Ganancia total],1),"")</f>
         <v/>
       </c>
@@ -2814,7 +2806,7 @@
         <f>IFERROR(INDEX(tbl_Productos[Producto],MATCH(B34,tbl_Productos[Ganancia total],0)),"")</f>
         <v/>
       </c>
-      <c r="B34" s="71">
+      <c r="B34" s="69">
         <f>IFERROR(LARGE(tbl_Productos[Ganancia total],2),"")</f>
         <v/>
       </c>
@@ -2824,7 +2816,7 @@
         <f>IFERROR(INDEX(tbl_Productos[Producto],MATCH(B35,tbl_Productos[Ganancia total],0)),"")</f>
         <v/>
       </c>
-      <c r="B35" s="71">
+      <c r="B35" s="69">
         <f>IFERROR(LARGE(tbl_Productos[Ganancia total],3),"")</f>
         <v/>
       </c>
@@ -2834,7 +2826,7 @@
         <f>IFERROR(INDEX(tbl_Productos[Producto],MATCH(B36,tbl_Productos[Ganancia total],0)),"")</f>
         <v/>
       </c>
-      <c r="B36" s="71">
+      <c r="B36" s="69">
         <f>IFERROR(LARGE(tbl_Productos[Ganancia total],4),"")</f>
         <v/>
       </c>
@@ -2844,7 +2836,7 @@
         <f>IFERROR(INDEX(tbl_Productos[Producto],MATCH(B37,tbl_Productos[Ganancia total],0)),"")</f>
         <v/>
       </c>
-      <c r="B37" s="71">
+      <c r="B37" s="69">
         <f>IFERROR(LARGE(tbl_Productos[Ganancia total],5),"")</f>
         <v/>
       </c>
@@ -2854,7 +2846,7 @@
         <f>IFERROR(INDEX(tbl_Productos[Producto],MATCH(B38,tbl_Productos[Ganancia total],0)),"")</f>
         <v/>
       </c>
-      <c r="B38" s="71">
+      <c r="B38" s="69">
         <f>IFERROR(LARGE(tbl_Productos[Ganancia total],6),"")</f>
         <v/>
       </c>
@@ -2864,7 +2856,7 @@
         <f>IFERROR(INDEX(tbl_Productos[Producto],MATCH(B39,tbl_Productos[Ganancia total],0)),"")</f>
         <v/>
       </c>
-      <c r="B39" s="71">
+      <c r="B39" s="69">
         <f>IFERROR(LARGE(tbl_Productos[Ganancia total],7),"")</f>
         <v/>
       </c>
@@ -2874,7 +2866,7 @@
         <f>IFERROR(INDEX(tbl_Productos[Producto],MATCH(B40,tbl_Productos[Ganancia total],0)),"")</f>
         <v/>
       </c>
-      <c r="B40" s="71">
+      <c r="B40" s="69">
         <f>IFERROR(LARGE(tbl_Productos[Ganancia total],8),"")</f>
         <v/>
       </c>
@@ -2885,7 +2877,7 @@
           <t>Otros</t>
         </is>
       </c>
-      <c r="B41" s="71">
+      <c r="B41" s="69">
         <f>MAX(SUM(tbl_Productos[Ganancia total])-SUM(B33:B40),0)</f>
         <v/>
       </c>
@@ -3025,901 +3017,901 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="72">
+      <c r="A21" s="70">
         <f>TODAY()-89</f>
         <v/>
       </c>
-      <c r="B21" s="71">
+      <c r="B21" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="72">
+      <c r="A22" s="70">
         <f>TODAY()-88</f>
         <v/>
       </c>
-      <c r="B22" s="71">
+      <c r="B22" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="72">
+      <c r="A23" s="70">
         <f>TODAY()-87</f>
         <v/>
       </c>
-      <c r="B23" s="71">
+      <c r="B23" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="72">
+      <c r="A24" s="70">
         <f>TODAY()-86</f>
         <v/>
       </c>
-      <c r="B24" s="71">
+      <c r="B24" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="72">
+      <c r="A25" s="70">
         <f>TODAY()-85</f>
         <v/>
       </c>
-      <c r="B25" s="71">
+      <c r="B25" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="72">
+      <c r="A26" s="70">
         <f>TODAY()-84</f>
         <v/>
       </c>
-      <c r="B26" s="71">
+      <c r="B26" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="72">
+      <c r="A27" s="70">
         <f>TODAY()-83</f>
         <v/>
       </c>
-      <c r="B27" s="71">
+      <c r="B27" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="72">
+      <c r="A28" s="70">
         <f>TODAY()-82</f>
         <v/>
       </c>
-      <c r="B28" s="71">
+      <c r="B28" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="72">
+      <c r="A29" s="70">
         <f>TODAY()-81</f>
         <v/>
       </c>
-      <c r="B29" s="71">
+      <c r="B29" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="72">
+      <c r="A30" s="70">
         <f>TODAY()-80</f>
         <v/>
       </c>
-      <c r="B30" s="71">
+      <c r="B30" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="72">
+      <c r="A31" s="70">
         <f>TODAY()-79</f>
         <v/>
       </c>
-      <c r="B31" s="71">
+      <c r="B31" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="72">
+      <c r="A32" s="70">
         <f>TODAY()-78</f>
         <v/>
       </c>
-      <c r="B32" s="71">
+      <c r="B32" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="72">
+      <c r="A33" s="70">
         <f>TODAY()-77</f>
         <v/>
       </c>
-      <c r="B33" s="71">
+      <c r="B33" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="72">
+      <c r="A34" s="70">
         <f>TODAY()-76</f>
         <v/>
       </c>
-      <c r="B34" s="71">
+      <c r="B34" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="72">
+      <c r="A35" s="70">
         <f>TODAY()-75</f>
         <v/>
       </c>
-      <c r="B35" s="71">
+      <c r="B35" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="72">
+      <c r="A36" s="70">
         <f>TODAY()-74</f>
         <v/>
       </c>
-      <c r="B36" s="71">
+      <c r="B36" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="72">
+      <c r="A37" s="70">
         <f>TODAY()-73</f>
         <v/>
       </c>
-      <c r="B37" s="71">
+      <c r="B37" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="72">
+      <c r="A38" s="70">
         <f>TODAY()-72</f>
         <v/>
       </c>
-      <c r="B38" s="71">
+      <c r="B38" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="72">
+      <c r="A39" s="70">
         <f>TODAY()-71</f>
         <v/>
       </c>
-      <c r="B39" s="71">
+      <c r="B39" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="72">
+      <c r="A40" s="70">
         <f>TODAY()-70</f>
         <v/>
       </c>
-      <c r="B40" s="71">
+      <c r="B40" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="72">
+      <c r="A41" s="70">
         <f>TODAY()-69</f>
         <v/>
       </c>
-      <c r="B41" s="71">
+      <c r="B41" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="72">
+      <c r="A42" s="70">
         <f>TODAY()-68</f>
         <v/>
       </c>
-      <c r="B42" s="71">
+      <c r="B42" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="72">
+      <c r="A43" s="70">
         <f>TODAY()-67</f>
         <v/>
       </c>
-      <c r="B43" s="71">
+      <c r="B43" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="72">
+      <c r="A44" s="70">
         <f>TODAY()-66</f>
         <v/>
       </c>
-      <c r="B44" s="71">
+      <c r="B44" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="72">
+      <c r="A45" s="70">
         <f>TODAY()-65</f>
         <v/>
       </c>
-      <c r="B45" s="71">
+      <c r="B45" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="72">
+      <c r="A46" s="70">
         <f>TODAY()-64</f>
         <v/>
       </c>
-      <c r="B46" s="71">
+      <c r="B46" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="72">
+      <c r="A47" s="70">
         <f>TODAY()-63</f>
         <v/>
       </c>
-      <c r="B47" s="71">
+      <c r="B47" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="72">
+      <c r="A48" s="70">
         <f>TODAY()-62</f>
         <v/>
       </c>
-      <c r="B48" s="71">
+      <c r="B48" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="72">
+      <c r="A49" s="70">
         <f>TODAY()-61</f>
         <v/>
       </c>
-      <c r="B49" s="71">
+      <c r="B49" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="72">
+      <c r="A50" s="70">
         <f>TODAY()-60</f>
         <v/>
       </c>
-      <c r="B50" s="71">
+      <c r="B50" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="72">
+      <c r="A51" s="70">
         <f>TODAY()-59</f>
         <v/>
       </c>
-      <c r="B51" s="71">
+      <c r="B51" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="72">
+      <c r="A52" s="70">
         <f>TODAY()-58</f>
         <v/>
       </c>
-      <c r="B52" s="71">
+      <c r="B52" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="72">
+      <c r="A53" s="70">
         <f>TODAY()-57</f>
         <v/>
       </c>
-      <c r="B53" s="71">
+      <c r="B53" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="72">
+      <c r="A54" s="70">
         <f>TODAY()-56</f>
         <v/>
       </c>
-      <c r="B54" s="71">
+      <c r="B54" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="72">
+      <c r="A55" s="70">
         <f>TODAY()-55</f>
         <v/>
       </c>
-      <c r="B55" s="71">
+      <c r="B55" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A55)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="72">
+      <c r="A56" s="70">
         <f>TODAY()-54</f>
         <v/>
       </c>
-      <c r="B56" s="71">
+      <c r="B56" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="72">
+      <c r="A57" s="70">
         <f>TODAY()-53</f>
         <v/>
       </c>
-      <c r="B57" s="71">
+      <c r="B57" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A57)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="72">
+      <c r="A58" s="70">
         <f>TODAY()-52</f>
         <v/>
       </c>
-      <c r="B58" s="71">
+      <c r="B58" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A58)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="72">
+      <c r="A59" s="70">
         <f>TODAY()-51</f>
         <v/>
       </c>
-      <c r="B59" s="71">
+      <c r="B59" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A59)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="72">
+      <c r="A60" s="70">
         <f>TODAY()-50</f>
         <v/>
       </c>
-      <c r="B60" s="71">
+      <c r="B60" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="72">
+      <c r="A61" s="70">
         <f>TODAY()-49</f>
         <v/>
       </c>
-      <c r="B61" s="71">
+      <c r="B61" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A61)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="72">
+      <c r="A62" s="70">
         <f>TODAY()-48</f>
         <v/>
       </c>
-      <c r="B62" s="71">
+      <c r="B62" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A62)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="72">
+      <c r="A63" s="70">
         <f>TODAY()-47</f>
         <v/>
       </c>
-      <c r="B63" s="71">
+      <c r="B63" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A63)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="72">
+      <c r="A64" s="70">
         <f>TODAY()-46</f>
         <v/>
       </c>
-      <c r="B64" s="71">
+      <c r="B64" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="72">
+      <c r="A65" s="70">
         <f>TODAY()-45</f>
         <v/>
       </c>
-      <c r="B65" s="71">
+      <c r="B65" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A65)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="72">
+      <c r="A66" s="70">
         <f>TODAY()-44</f>
         <v/>
       </c>
-      <c r="B66" s="71">
+      <c r="B66" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A66)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="72">
+      <c r="A67" s="70">
         <f>TODAY()-43</f>
         <v/>
       </c>
-      <c r="B67" s="71">
+      <c r="B67" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A67)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="72">
+      <c r="A68" s="70">
         <f>TODAY()-42</f>
         <v/>
       </c>
-      <c r="B68" s="71">
+      <c r="B68" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A68)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="72">
+      <c r="A69" s="70">
         <f>TODAY()-41</f>
         <v/>
       </c>
-      <c r="B69" s="71">
+      <c r="B69" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A69)</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="72">
+      <c r="A70" s="70">
         <f>TODAY()-40</f>
         <v/>
       </c>
-      <c r="B70" s="71">
+      <c r="B70" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A70)</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="72">
+      <c r="A71" s="70">
         <f>TODAY()-39</f>
         <v/>
       </c>
-      <c r="B71" s="71">
+      <c r="B71" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A71)</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="72">
+      <c r="A72" s="70">
         <f>TODAY()-38</f>
         <v/>
       </c>
-      <c r="B72" s="71">
+      <c r="B72" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A72)</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="72">
+      <c r="A73" s="70">
         <f>TODAY()-37</f>
         <v/>
       </c>
-      <c r="B73" s="71">
+      <c r="B73" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A73)</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="72">
+      <c r="A74" s="70">
         <f>TODAY()-36</f>
         <v/>
       </c>
-      <c r="B74" s="71">
+      <c r="B74" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A74)</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="72">
+      <c r="A75" s="70">
         <f>TODAY()-35</f>
         <v/>
       </c>
-      <c r="B75" s="71">
+      <c r="B75" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A75)</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="72">
+      <c r="A76" s="70">
         <f>TODAY()-34</f>
         <v/>
       </c>
-      <c r="B76" s="71">
+      <c r="B76" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A76)</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="72">
+      <c r="A77" s="70">
         <f>TODAY()-33</f>
         <v/>
       </c>
-      <c r="B77" s="71">
+      <c r="B77" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A77)</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="72">
+      <c r="A78" s="70">
         <f>TODAY()-32</f>
         <v/>
       </c>
-      <c r="B78" s="71">
+      <c r="B78" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A78)</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="72">
+      <c r="A79" s="70">
         <f>TODAY()-31</f>
         <v/>
       </c>
-      <c r="B79" s="71">
+      <c r="B79" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A79)</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="72">
+      <c r="A80" s="70">
         <f>TODAY()-30</f>
         <v/>
       </c>
-      <c r="B80" s="71">
+      <c r="B80" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A80)</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="72">
+      <c r="A81" s="70">
         <f>TODAY()-29</f>
         <v/>
       </c>
-      <c r="B81" s="71">
+      <c r="B81" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A81)</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="72">
+      <c r="A82" s="70">
         <f>TODAY()-28</f>
         <v/>
       </c>
-      <c r="B82" s="71">
+      <c r="B82" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A82)</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="72">
+      <c r="A83" s="70">
         <f>TODAY()-27</f>
         <v/>
       </c>
-      <c r="B83" s="71">
+      <c r="B83" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A83)</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="72">
+      <c r="A84" s="70">
         <f>TODAY()-26</f>
         <v/>
       </c>
-      <c r="B84" s="71">
+      <c r="B84" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A84)</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="72">
+      <c r="A85" s="70">
         <f>TODAY()-25</f>
         <v/>
       </c>
-      <c r="B85" s="71">
+      <c r="B85" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A85)</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="72">
+      <c r="A86" s="70">
         <f>TODAY()-24</f>
         <v/>
       </c>
-      <c r="B86" s="71">
+      <c r="B86" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A86)</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="72">
+      <c r="A87" s="70">
         <f>TODAY()-23</f>
         <v/>
       </c>
-      <c r="B87" s="71">
+      <c r="B87" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A87)</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="72">
+      <c r="A88" s="70">
         <f>TODAY()-22</f>
         <v/>
       </c>
-      <c r="B88" s="71">
+      <c r="B88" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A88)</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="72">
+      <c r="A89" s="70">
         <f>TODAY()-21</f>
         <v/>
       </c>
-      <c r="B89" s="71">
+      <c r="B89" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A89)</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="72">
+      <c r="A90" s="70">
         <f>TODAY()-20</f>
         <v/>
       </c>
-      <c r="B90" s="71">
+      <c r="B90" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A90)</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="72">
+      <c r="A91" s="70">
         <f>TODAY()-19</f>
         <v/>
       </c>
-      <c r="B91" s="71">
+      <c r="B91" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A91)</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="72">
+      <c r="A92" s="70">
         <f>TODAY()-18</f>
         <v/>
       </c>
-      <c r="B92" s="71">
+      <c r="B92" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A92)</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="72">
+      <c r="A93" s="70">
         <f>TODAY()-17</f>
         <v/>
       </c>
-      <c r="B93" s="71">
+      <c r="B93" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A93)</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="72">
+      <c r="A94" s="70">
         <f>TODAY()-16</f>
         <v/>
       </c>
-      <c r="B94" s="71">
+      <c r="B94" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A94)</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="72">
+      <c r="A95" s="70">
         <f>TODAY()-15</f>
         <v/>
       </c>
-      <c r="B95" s="71">
+      <c r="B95" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A95)</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="72">
+      <c r="A96" s="70">
         <f>TODAY()-14</f>
         <v/>
       </c>
-      <c r="B96" s="71">
+      <c r="B96" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A96)</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="72">
+      <c r="A97" s="70">
         <f>TODAY()-13</f>
         <v/>
       </c>
-      <c r="B97" s="71">
+      <c r="B97" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A97)</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="72">
+      <c r="A98" s="70">
         <f>TODAY()-12</f>
         <v/>
       </c>
-      <c r="B98" s="71">
+      <c r="B98" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A98)</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="72">
+      <c r="A99" s="70">
         <f>TODAY()-11</f>
         <v/>
       </c>
-      <c r="B99" s="71">
+      <c r="B99" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A99)</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="72">
+      <c r="A100" s="70">
         <f>TODAY()-10</f>
         <v/>
       </c>
-      <c r="B100" s="71">
+      <c r="B100" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A100)</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="72">
+      <c r="A101" s="70">
         <f>TODAY()-9</f>
         <v/>
       </c>
-      <c r="B101" s="71">
+      <c r="B101" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A101)</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="72">
+      <c r="A102" s="70">
         <f>TODAY()-8</f>
         <v/>
       </c>
-      <c r="B102" s="71">
+      <c r="B102" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A102)</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="72">
+      <c r="A103" s="70">
         <f>TODAY()-7</f>
         <v/>
       </c>
-      <c r="B103" s="71">
+      <c r="B103" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A103)</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="72">
+      <c r="A104" s="70">
         <f>TODAY()-6</f>
         <v/>
       </c>
-      <c r="B104" s="71">
+      <c r="B104" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A104)</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="72">
+      <c r="A105" s="70">
         <f>TODAY()-5</f>
         <v/>
       </c>
-      <c r="B105" s="71">
+      <c r="B105" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A105)</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="72">
+      <c r="A106" s="70">
         <f>TODAY()-4</f>
         <v/>
       </c>
-      <c r="B106" s="71">
+      <c r="B106" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A106)</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="72">
+      <c r="A107" s="70">
         <f>TODAY()-3</f>
         <v/>
       </c>
-      <c r="B107" s="71">
+      <c r="B107" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A107)</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="72">
+      <c r="A108" s="70">
         <f>TODAY()-2</f>
         <v/>
       </c>
-      <c r="B108" s="71">
+      <c r="B108" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A108)</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="72">
+      <c r="A109" s="70">
         <f>TODAY()-1</f>
         <v/>
       </c>
-      <c r="B109" s="71">
+      <c r="B109" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A109)</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="72">
+      <c r="A110" s="70">
         <f>TODAY()-0</f>
         <v/>
       </c>
-      <c r="B110" s="71">
+      <c r="B110" s="69">
         <f>SUMIFS(tbl_Ventas[Ganancia],tbl_Ventas[Fecha],A110)</f>
         <v/>
       </c>
@@ -3980,27 +3972,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="70" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>RuleID</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="68" t="inlineStr">
         <is>
           <t>Condición</t>
         </is>
       </c>
-      <c r="C1" s="70" t="inlineStr">
+      <c r="C1" s="68" t="inlineStr">
         <is>
           <t>Plantilla</t>
         </is>
       </c>
-      <c r="D1" s="70" t="inlineStr">
+      <c r="D1" s="68" t="inlineStr">
         <is>
           <t>Prioridad</t>
         </is>
       </c>
-      <c r="E1" s="70" t="inlineStr">
+      <c r="E1" s="68" t="inlineStr">
         <is>
           <t>Activa</t>
         </is>
@@ -4825,89 +4817,89 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="73" t="inlineStr">
+      <c r="A1" s="71" t="inlineStr">
         <is>
           <t>Demo · Productos</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="74" t="inlineStr">
+      <c r="B2" s="72" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="C2" s="74" t="inlineStr">
+      <c r="C2" s="72" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="D2" s="74" t="inlineStr">
+      <c r="D2" s="72" t="inlineStr">
         <is>
           <t>Precio de venta</t>
         </is>
       </c>
-      <c r="E2" s="74" t="inlineStr">
+      <c r="E2" s="72" t="inlineStr">
         <is>
           <t>Costo del producto</t>
         </is>
       </c>
-      <c r="F2" s="74" t="inlineStr">
+      <c r="F2" s="72" t="inlineStr">
         <is>
           <t>Comisión %</t>
         </is>
       </c>
-      <c r="G2" s="74" t="inlineStr">
+      <c r="G2" s="72" t="inlineStr">
         <is>
           <t>Packaging</t>
         </is>
       </c>
-      <c r="H2" s="74" t="inlineStr">
+      <c r="H2" s="72" t="inlineStr">
         <is>
           <t>Envío / costo asociado</t>
         </is>
       </c>
-      <c r="I2" s="74" t="inlineStr">
+      <c r="I2" s="72" t="inlineStr">
         <is>
           <t>Publicidad atribuida</t>
         </is>
       </c>
-      <c r="J2" s="74" t="inlineStr">
+      <c r="J2" s="72" t="inlineStr">
         <is>
           <t>Otros costos</t>
         </is>
       </c>
-      <c r="K2" s="74" t="inlineStr">
+      <c r="K2" s="72" t="inlineStr">
         <is>
           <t>Costo real de venta</t>
         </is>
       </c>
-      <c r="L2" s="74" t="inlineStr">
+      <c r="L2" s="72" t="inlineStr">
         <is>
           <t>Ganancia por unidad</t>
         </is>
       </c>
-      <c r="M2" s="74" t="inlineStr">
+      <c r="M2" s="72" t="inlineStr">
         <is>
           <t>Margen</t>
         </is>
       </c>
-      <c r="N2" s="74" t="inlineStr">
+      <c r="N2" s="72" t="inlineStr">
         <is>
           <t>Unidades vendidas</t>
         </is>
       </c>
-      <c r="O2" s="74" t="inlineStr">
+      <c r="O2" s="72" t="inlineStr">
         <is>
           <t>Ganancia total</t>
         </is>
       </c>
-      <c r="Q2" s="73" t="inlineStr">
+      <c r="Q2" s="71" t="inlineStr">
         <is>
           <t>Demo · Gastos</t>
         </is>
       </c>
-      <c r="W2" s="73" t="inlineStr">
+      <c r="W2" s="71" t="inlineStr">
         <is>
           <t>Demo · Objetivos</t>
         </is>
@@ -4957,35 +4949,35 @@
         <f>IF(D3=0,"",L3/D3)</f>
         <v/>
       </c>
-      <c r="N3" s="75">
+      <c r="N3" s="73">
         <f>SUMIFS($D$22:$D$132,$C$22:$C$132,B3)</f>
         <v/>
       </c>
-      <c r="O3" s="71">
+      <c r="O3" s="69">
         <f>SUMIFS($L$22:$L$132,$C$22:$C$132,B3)</f>
         <v/>
       </c>
-      <c r="Q3" s="74" t="inlineStr">
+      <c r="Q3" s="72" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="R3" s="74" t="inlineStr">
+      <c r="R3" s="72" t="inlineStr">
         <is>
           <t>Categoría</t>
         </is>
       </c>
-      <c r="S3" s="74" t="inlineStr">
+      <c r="S3" s="72" t="inlineStr">
         <is>
           <t>Descripción</t>
         </is>
       </c>
-      <c r="T3" s="74" t="inlineStr">
+      <c r="T3" s="72" t="inlineStr">
         <is>
           <t>Importe</t>
         </is>
       </c>
-      <c r="U3" s="74" t="inlineStr">
+      <c r="U3" s="72" t="inlineStr">
         <is>
           <t>Tipo de gasto</t>
         </is>
@@ -5045,15 +5037,15 @@
         <f>IF(D4=0,"",L4/D4)</f>
         <v/>
       </c>
-      <c r="N4" s="75">
+      <c r="N4" s="73">
         <f>SUMIFS($D$22:$D$132,$C$22:$C$132,B4)</f>
         <v/>
       </c>
-      <c r="O4" s="71">
+      <c r="O4" s="69">
         <f>SUMIFS($L$22:$L$132,$C$22:$C$132,B4)</f>
         <v/>
       </c>
-      <c r="Q4" s="72" t="n">
+      <c r="Q4" s="70" t="n">
         <v>46270</v>
       </c>
       <c r="R4" t="inlineStr">
@@ -5074,7 +5066,7 @@
           <t>Fijo</t>
         </is>
       </c>
-      <c r="W4" s="72" t="n">
+      <c r="W4" s="70" t="n">
         <v>46266</v>
       </c>
       <c r="X4" t="n">
@@ -5125,15 +5117,15 @@
         <f>IF(D5=0,"",L5/D5)</f>
         <v/>
       </c>
-      <c r="N5" s="75">
+      <c r="N5" s="73">
         <f>SUMIFS($D$22:$D$132,$C$22:$C$132,B5)</f>
         <v/>
       </c>
-      <c r="O5" s="71">
+      <c r="O5" s="69">
         <f>SUMIFS($L$22:$L$132,$C$22:$C$132,B5)</f>
         <v/>
       </c>
-      <c r="Q5" s="72" t="n">
+      <c r="Q5" s="70" t="n">
         <v>46272</v>
       </c>
       <c r="R5" t="inlineStr">
@@ -5199,15 +5191,15 @@
         <f>IF(D6=0,"",L6/D6)</f>
         <v/>
       </c>
-      <c r="N6" s="75">
+      <c r="N6" s="73">
         <f>SUMIFS($D$22:$D$132,$C$22:$C$132,B6)</f>
         <v/>
       </c>
-      <c r="O6" s="71">
+      <c r="O6" s="69">
         <f>SUMIFS($L$22:$L$132,$C$22:$C$132,B6)</f>
         <v/>
       </c>
-      <c r="Q6" s="72" t="n">
+      <c r="Q6" s="70" t="n">
         <v>46280</v>
       </c>
       <c r="R6" t="inlineStr">
@@ -5273,15 +5265,15 @@
         <f>IF(D7=0,"",L7/D7)</f>
         <v/>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="73">
         <f>SUMIFS($D$22:$D$132,$C$22:$C$132,B7)</f>
         <v/>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="69">
         <f>SUMIFS($L$22:$L$132,$C$22:$C$132,B7)</f>
         <v/>
       </c>
-      <c r="Q7" s="72" t="n">
+      <c r="Q7" s="70" t="n">
         <v>46240</v>
       </c>
       <c r="R7" t="inlineStr">
@@ -5347,15 +5339,15 @@
         <f>IF(D8=0,"",L8/D8)</f>
         <v/>
       </c>
-      <c r="N8" s="75">
+      <c r="N8" s="73">
         <f>SUMIFS($D$22:$D$132,$C$22:$C$132,B8)</f>
         <v/>
       </c>
-      <c r="O8" s="71">
+      <c r="O8" s="69">
         <f>SUMIFS($L$22:$L$132,$C$22:$C$132,B8)</f>
         <v/>
       </c>
-      <c r="Q8" s="72" t="n">
+      <c r="Q8" s="70" t="n">
         <v>46242</v>
       </c>
       <c r="R8" t="inlineStr">
@@ -5421,15 +5413,15 @@
         <f>IF(D9=0,"",L9/D9)</f>
         <v/>
       </c>
-      <c r="N9" s="75">
+      <c r="N9" s="73">
         <f>SUMIFS($D$22:$D$132,$C$22:$C$132,B9)</f>
         <v/>
       </c>
-      <c r="O9" s="71">
+      <c r="O9" s="69">
         <f>SUMIFS($L$22:$L$132,$C$22:$C$132,B9)</f>
         <v/>
       </c>
-      <c r="Q9" s="72" t="n">
+      <c r="Q9" s="70" t="n">
         <v>46250</v>
       </c>
       <c r="R9" t="inlineStr">
@@ -5495,15 +5487,15 @@
         <f>IF(D10=0,"",L10/D10)</f>
         <v/>
       </c>
-      <c r="N10" s="75">
+      <c r="N10" s="73">
         <f>SUMIFS($D$22:$D$132,$C$22:$C$132,B10)</f>
         <v/>
       </c>
-      <c r="O10" s="71">
+      <c r="O10" s="69">
         <f>SUMIFS($L$22:$L$132,$C$22:$C$132,B10)</f>
         <v/>
       </c>
-      <c r="Q10" s="72" t="n">
+      <c r="Q10" s="70" t="n">
         <v>46210</v>
       </c>
       <c r="R10" t="inlineStr">
@@ -5526,7 +5518,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="Q11" s="72" t="n">
+      <c r="Q11" s="70" t="n">
         <v>46212</v>
       </c>
       <c r="R11" t="inlineStr">
@@ -5549,7 +5541,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="Q12" s="72" t="n">
+      <c r="Q12" s="70" t="n">
         <v>46220</v>
       </c>
       <c r="R12" t="inlineStr">
@@ -5572,7 +5564,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="Q13" s="72" t="n">
+      <c r="Q13" s="70" t="n">
         <v>46256</v>
       </c>
       <c r="R13" t="inlineStr">
@@ -5595,7 +5587,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="Q14" s="72" t="n">
+      <c r="Q14" s="70" t="n">
         <v>46271</v>
       </c>
       <c r="R14" t="inlineStr">
@@ -5625,64 +5617,64 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="74" t="inlineStr">
+      <c r="B21" s="72" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="C21" s="74" t="inlineStr">
+      <c r="C21" s="72" t="inlineStr">
         <is>
           <t>Producto</t>
         </is>
       </c>
-      <c r="D21" s="74" t="inlineStr">
+      <c r="D21" s="72" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="E21" s="74" t="inlineStr">
+      <c r="E21" s="72" t="inlineStr">
         <is>
           <t>Precio de venta</t>
         </is>
       </c>
-      <c r="F21" s="74" t="inlineStr">
+      <c r="F21" s="72" t="inlineStr">
         <is>
           <t>Canal</t>
         </is>
       </c>
-      <c r="G21" s="74" t="inlineStr">
+      <c r="G21" s="72" t="inlineStr">
         <is>
           <t>Comisión %</t>
         </is>
       </c>
-      <c r="H21" s="74" t="inlineStr">
+      <c r="H21" s="72" t="inlineStr">
         <is>
           <t>Descuento</t>
         </is>
       </c>
-      <c r="I21" s="74" t="inlineStr">
+      <c r="I21" s="72" t="inlineStr">
         <is>
           <t>Otros costos</t>
         </is>
       </c>
-      <c r="J21" s="74" t="inlineStr">
+      <c r="J21" s="72" t="inlineStr">
         <is>
           <t>Venta total</t>
         </is>
       </c>
-      <c r="K21" s="74" t="inlineStr">
+      <c r="K21" s="72" t="inlineStr">
         <is>
           <t>Costo total de la venta</t>
         </is>
       </c>
-      <c r="L21" s="74" t="inlineStr">
+      <c r="L21" s="72" t="inlineStr">
         <is>
           <t>Ganancia</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="72" t="n">
+      <c r="B22" s="70" t="n">
         <v>46187</v>
       </c>
       <c r="C22" t="inlineStr">
@@ -5726,7 +5718,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="72" t="n">
+      <c r="B23" s="70" t="n">
         <v>46187</v>
       </c>
       <c r="C23" t="inlineStr">
@@ -5770,7 +5762,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="72" t="n">
+      <c r="B24" s="70" t="n">
         <v>46189</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -5814,7 +5806,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="72" t="n">
+      <c r="B25" s="70" t="n">
         <v>46190</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -5858,7 +5850,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="72" t="n">
+      <c r="B26" s="70" t="n">
         <v>46192</v>
       </c>
       <c r="C26" t="inlineStr">
@@ -5902,7 +5894,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="72" t="n">
+      <c r="B27" s="70" t="n">
         <v>46193</v>
       </c>
       <c r="C27" t="inlineStr">
@@ -5946,7 +5938,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="72" t="n">
+      <c r="B28" s="70" t="n">
         <v>46193</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -5990,7 +5982,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="72" t="n">
+      <c r="B29" s="70" t="n">
         <v>46195</v>
       </c>
       <c r="C29" t="inlineStr">
@@ -6034,7 +6026,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="72" t="n">
+      <c r="B30" s="70" t="n">
         <v>46196</v>
       </c>
       <c r="C30" t="inlineStr">
@@ -6078,7 +6070,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="72" t="n">
+      <c r="B31" s="70" t="n">
         <v>46198</v>
       </c>
       <c r="C31" t="inlineStr">
@@ -6122,7 +6114,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="72" t="n">
+      <c r="B32" s="70" t="n">
         <v>46199</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -6166,7 +6158,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="72" t="n">
+      <c r="B33" s="70" t="n">
         <v>46199</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -6210,7 +6202,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="72" t="n">
+      <c r="B34" s="70" t="n">
         <v>46199</v>
       </c>
       <c r="C34" t="inlineStr">
@@ -6254,7 +6246,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="72" t="n">
+      <c r="B35" s="70" t="n">
         <v>46200</v>
       </c>
       <c r="C35" t="inlineStr">
@@ -6298,7 +6290,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="72" t="n">
+      <c r="B36" s="70" t="n">
         <v>46200</v>
       </c>
       <c r="C36" t="inlineStr">
@@ -6342,7 +6334,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="72" t="n">
+      <c r="B37" s="70" t="n">
         <v>46200</v>
       </c>
       <c r="C37" t="inlineStr">
@@ -6386,7 +6378,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="72" t="n">
+      <c r="B38" s="70" t="n">
         <v>46201</v>
       </c>
       <c r="C38" t="inlineStr">
@@ -6430,7 +6422,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="72" t="n">
+      <c r="B39" s="70" t="n">
         <v>46201</v>
       </c>
       <c r="C39" t="inlineStr">
@@ -6474,7 +6466,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="72" t="n">
+      <c r="B40" s="70" t="n">
         <v>46202</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -6518,7 +6510,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="72" t="n">
+      <c r="B41" s="70" t="n">
         <v>46203</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -6562,7 +6554,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="72" t="n">
+      <c r="B42" s="70" t="n">
         <v>46204</v>
       </c>
       <c r="C42" t="inlineStr">
@@ -6606,7 +6598,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="72" t="n">
+      <c r="B43" s="70" t="n">
         <v>46204</v>
       </c>
       <c r="C43" t="inlineStr">
@@ -6650,7 +6642,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="72" t="n">
+      <c r="B44" s="70" t="n">
         <v>46206</v>
       </c>
       <c r="C44" t="inlineStr">
@@ -6694,7 +6686,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="72" t="n">
+      <c r="B45" s="70" t="n">
         <v>46207</v>
       </c>
       <c r="C45" t="inlineStr">
@@ -6738,7 +6730,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="72" t="n">
+      <c r="B46" s="70" t="n">
         <v>46207</v>
       </c>
       <c r="C46" t="inlineStr">
@@ -6782,7 +6774,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="72" t="n">
+      <c r="B47" s="70" t="n">
         <v>46208</v>
       </c>
       <c r="C47" t="inlineStr">
@@ -6826,7 +6818,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="72" t="n">
+      <c r="B48" s="70" t="n">
         <v>46208</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -6870,7 +6862,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="72" t="n">
+      <c r="B49" s="70" t="n">
         <v>46210</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -6914,7 +6906,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="72" t="n">
+      <c r="B50" s="70" t="n">
         <v>46211</v>
       </c>
       <c r="C50" t="inlineStr">
@@ -6958,7 +6950,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="72" t="n">
+      <c r="B51" s="70" t="n">
         <v>46211</v>
       </c>
       <c r="C51" t="inlineStr">
@@ -7002,7 +6994,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="72" t="n">
+      <c r="B52" s="70" t="n">
         <v>46211</v>
       </c>
       <c r="C52" t="inlineStr">
@@ -7046,7 +7038,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="72" t="n">
+      <c r="B53" s="70" t="n">
         <v>46213</v>
       </c>
       <c r="C53" t="inlineStr">
@@ -7090,7 +7082,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="72" t="n">
+      <c r="B54" s="70" t="n">
         <v>46213</v>
       </c>
       <c r="C54" t="inlineStr">
@@ -7134,7 +7126,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="72" t="n">
+      <c r="B55" s="70" t="n">
         <v>46213</v>
       </c>
       <c r="C55" t="inlineStr">
@@ -7178,7 +7170,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="72" t="n">
+      <c r="B56" s="70" t="n">
         <v>46214</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -7222,7 +7214,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="72" t="n">
+      <c r="B57" s="70" t="n">
         <v>46218</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -7266,7 +7258,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="72" t="n">
+      <c r="B58" s="70" t="n">
         <v>46220</v>
       </c>
       <c r="C58" t="inlineStr">
@@ -7310,7 +7302,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="72" t="n">
+      <c r="B59" s="70" t="n">
         <v>46221</v>
       </c>
       <c r="C59" t="inlineStr">
@@ -7354,7 +7346,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="72" t="n">
+      <c r="B60" s="70" t="n">
         <v>46221</v>
       </c>
       <c r="C60" t="inlineStr">
@@ -7398,7 +7390,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="72" t="n">
+      <c r="B61" s="70" t="n">
         <v>46223</v>
       </c>
       <c r="C61" t="inlineStr">
@@ -7442,7 +7434,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="72" t="n">
+      <c r="B62" s="70" t="n">
         <v>46223</v>
       </c>
       <c r="C62" t="inlineStr">
@@ -7486,7 +7478,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="72" t="n">
+      <c r="B63" s="70" t="n">
         <v>46225</v>
       </c>
       <c r="C63" t="inlineStr">
@@ -7530,7 +7522,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="72" t="n">
+      <c r="B64" s="70" t="n">
         <v>46226</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -7574,7 +7566,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="72" t="n">
+      <c r="B65" s="70" t="n">
         <v>46226</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -7618,7 +7610,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="72" t="n">
+      <c r="B66" s="70" t="n">
         <v>46227</v>
       </c>
       <c r="C66" t="inlineStr">
@@ -7662,7 +7654,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="72" t="n">
+      <c r="B67" s="70" t="n">
         <v>46228</v>
       </c>
       <c r="C67" t="inlineStr">
@@ -7706,7 +7698,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="72" t="n">
+      <c r="B68" s="70" t="n">
         <v>46231</v>
       </c>
       <c r="C68" t="inlineStr">
@@ -7750,7 +7742,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="72" t="n">
+      <c r="B69" s="70" t="n">
         <v>46232</v>
       </c>
       <c r="C69" t="inlineStr">
@@ -7794,7 +7786,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="72" t="n">
+      <c r="B70" s="70" t="n">
         <v>46232</v>
       </c>
       <c r="C70" t="inlineStr">
@@ -7838,7 +7830,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="72" t="n">
+      <c r="B71" s="70" t="n">
         <v>46232</v>
       </c>
       <c r="C71" t="inlineStr">
@@ -7882,7 +7874,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="72" t="n">
+      <c r="B72" s="70" t="n">
         <v>46234</v>
       </c>
       <c r="C72" t="inlineStr">
@@ -7926,7 +7918,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="72" t="n">
+      <c r="B73" s="70" t="n">
         <v>46234</v>
       </c>
       <c r="C73" t="inlineStr">
@@ -7970,7 +7962,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="72" t="n">
+      <c r="B74" s="70" t="n">
         <v>46234</v>
       </c>
       <c r="C74" t="inlineStr">
@@ -8014,7 +8006,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="72" t="n">
+      <c r="B75" s="70" t="n">
         <v>46235</v>
       </c>
       <c r="C75" t="inlineStr">
@@ -8058,7 +8050,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="72" t="n">
+      <c r="B76" s="70" t="n">
         <v>46235</v>
       </c>
       <c r="C76" t="inlineStr">
@@ -8102,7 +8094,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="72" t="n">
+      <c r="B77" s="70" t="n">
         <v>46236</v>
       </c>
       <c r="C77" t="inlineStr">
@@ -8146,7 +8138,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="72" t="n">
+      <c r="B78" s="70" t="n">
         <v>46236</v>
       </c>
       <c r="C78" t="inlineStr">
@@ -8190,7 +8182,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="72" t="n">
+      <c r="B79" s="70" t="n">
         <v>46236</v>
       </c>
       <c r="C79" t="inlineStr">
@@ -8234,7 +8226,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="72" t="n">
+      <c r="B80" s="70" t="n">
         <v>46238</v>
       </c>
       <c r="C80" t="inlineStr">
@@ -8278,7 +8270,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="72" t="n">
+      <c r="B81" s="70" t="n">
         <v>46239</v>
       </c>
       <c r="C81" t="inlineStr">
@@ -8322,7 +8314,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="72" t="n">
+      <c r="B82" s="70" t="n">
         <v>46240</v>
       </c>
       <c r="C82" t="inlineStr">
@@ -8366,7 +8358,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="72" t="n">
+      <c r="B83" s="70" t="n">
         <v>46240</v>
       </c>
       <c r="C83" t="inlineStr">
@@ -8410,7 +8402,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="72" t="n">
+      <c r="B84" s="70" t="n">
         <v>46241</v>
       </c>
       <c r="C84" t="inlineStr">
@@ -8454,7 +8446,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="72" t="n">
+      <c r="B85" s="70" t="n">
         <v>46241</v>
       </c>
       <c r="C85" t="inlineStr">
@@ -8498,7 +8490,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="72" t="n">
+      <c r="B86" s="70" t="n">
         <v>46242</v>
       </c>
       <c r="C86" t="inlineStr">
@@ -8542,7 +8534,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" s="72" t="n">
+      <c r="B87" s="70" t="n">
         <v>46243</v>
       </c>
       <c r="C87" t="inlineStr">
@@ -8586,7 +8578,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="72" t="n">
+      <c r="B88" s="70" t="n">
         <v>46243</v>
       </c>
       <c r="C88" t="inlineStr">
@@ -8630,7 +8622,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="72" t="n">
+      <c r="B89" s="70" t="n">
         <v>46243</v>
       </c>
       <c r="C89" t="inlineStr">
@@ -8674,7 +8666,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="72" t="n">
+      <c r="B90" s="70" t="n">
         <v>46244</v>
       </c>
       <c r="C90" t="inlineStr">
@@ -8718,7 +8710,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="72" t="n">
+      <c r="B91" s="70" t="n">
         <v>46245</v>
       </c>
       <c r="C91" t="inlineStr">
@@ -8762,7 +8754,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="72" t="n">
+      <c r="B92" s="70" t="n">
         <v>46245</v>
       </c>
       <c r="C92" t="inlineStr">
@@ -8806,7 +8798,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="72" t="n">
+      <c r="B93" s="70" t="n">
         <v>46245</v>
       </c>
       <c r="C93" t="inlineStr">
@@ -8850,7 +8842,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="72" t="n">
+      <c r="B94" s="70" t="n">
         <v>46246</v>
       </c>
       <c r="C94" t="inlineStr">
@@ -8894,7 +8886,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="72" t="n">
+      <c r="B95" s="70" t="n">
         <v>46246</v>
       </c>
       <c r="C95" t="inlineStr">
@@ -8938,7 +8930,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="72" t="n">
+      <c r="B96" s="70" t="n">
         <v>46246</v>
       </c>
       <c r="C96" t="inlineStr">
@@ -8982,7 +8974,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="72" t="n">
+      <c r="B97" s="70" t="n">
         <v>46248</v>
       </c>
       <c r="C97" t="inlineStr">
@@ -9026,7 +9018,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="72" t="n">
+      <c r="B98" s="70" t="n">
         <v>46249</v>
       </c>
       <c r="C98" t="inlineStr">
@@ -9070,7 +9062,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="72" t="n">
+      <c r="B99" s="70" t="n">
         <v>46250</v>
       </c>
       <c r="C99" t="inlineStr">
@@ -9114,7 +9106,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="72" t="n">
+      <c r="B100" s="70" t="n">
         <v>46252</v>
       </c>
       <c r="C100" t="inlineStr">
@@ -9158,7 +9150,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="72" t="n">
+      <c r="B101" s="70" t="n">
         <v>46252</v>
       </c>
       <c r="C101" t="inlineStr">
@@ -9202,7 +9194,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="B102" s="72" t="n">
+      <c r="B102" s="70" t="n">
         <v>46253</v>
       </c>
       <c r="C102" t="inlineStr">
@@ -9246,7 +9238,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="B103" s="72" t="n">
+      <c r="B103" s="70" t="n">
         <v>46253</v>
       </c>
       <c r="C103" t="inlineStr">
@@ -9290,7 +9282,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="B104" s="72" t="n">
+      <c r="B104" s="70" t="n">
         <v>46254</v>
       </c>
       <c r="C104" t="inlineStr">
@@ -9334,7 +9326,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="B105" s="72" t="n">
+      <c r="B105" s="70" t="n">
         <v>46254</v>
       </c>
       <c r="C105" t="inlineStr">
@@ -9378,7 +9370,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="72" t="n">
+      <c r="B106" s="70" t="n">
         <v>46254</v>
       </c>
       <c r="C106" t="inlineStr">
@@ -9422,7 +9414,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="72" t="n">
+      <c r="B107" s="70" t="n">
         <v>46255</v>
       </c>
       <c r="C107" t="inlineStr">
@@ -9466,7 +9458,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="B108" s="72" t="n">
+      <c r="B108" s="70" t="n">
         <v>46256</v>
       </c>
       <c r="C108" t="inlineStr">
@@ -9510,7 +9502,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="72" t="n">
+      <c r="B109" s="70" t="n">
         <v>46256</v>
       </c>
       <c r="C109" t="inlineStr">
@@ -9554,7 +9546,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="72" t="n">
+      <c r="B110" s="70" t="n">
         <v>46257</v>
       </c>
       <c r="C110" t="inlineStr">
@@ -9598,7 +9590,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="72" t="n">
+      <c r="B111" s="70" t="n">
         <v>46257</v>
       </c>
       <c r="C111" t="inlineStr">
@@ -9642,7 +9634,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="B112" s="72" t="n">
+      <c r="B112" s="70" t="n">
         <v>46259</v>
       </c>
       <c r="C112" t="inlineStr">
@@ -9686,7 +9678,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="B113" s="72" t="n">
+      <c r="B113" s="70" t="n">
         <v>46261</v>
       </c>
       <c r="C113" t="inlineStr">
@@ -9730,7 +9722,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="72" t="n">
+      <c r="B114" s="70" t="n">
         <v>46261</v>
       </c>
       <c r="C114" t="inlineStr">
@@ -9779,7 +9771,7 @@
           <t>Demo · Ganancia por producto (top 8)</t>
         </is>
       </c>
-      <c r="B115" s="72" t="n">
+      <c r="B115" s="70" t="n">
         <v>46261</v>
       </c>
       <c r="C115" t="inlineStr">
@@ -9827,7 +9819,7 @@
         <f>IFERROR(INDEX($B$3:$B$10,MATCH(B116,$O$3:$O$10,0)),"")</f>
         <v/>
       </c>
-      <c r="B116" s="71">
+      <c r="B116" s="69">
         <f>IFERROR(LARGE($O$3:$O$10,1),"")</f>
         <v/>
       </c>
@@ -9876,7 +9868,7 @@
         <f>IFERROR(INDEX($B$3:$B$10,MATCH(B117,$O$3:$O$10,0)),"")</f>
         <v/>
       </c>
-      <c r="B117" s="71">
+      <c r="B117" s="69">
         <f>IFERROR(LARGE($O$3:$O$10,2),"")</f>
         <v/>
       </c>
@@ -9925,7 +9917,7 @@
         <f>IFERROR(INDEX($B$3:$B$10,MATCH(B118,$O$3:$O$10,0)),"")</f>
         <v/>
       </c>
-      <c r="B118" s="71">
+      <c r="B118" s="69">
         <f>IFERROR(LARGE($O$3:$O$10,3),"")</f>
         <v/>
       </c>
@@ -9974,7 +9966,7 @@
         <f>IFERROR(INDEX($B$3:$B$10,MATCH(B119,$O$3:$O$10,0)),"")</f>
         <v/>
       </c>
-      <c r="B119" s="71">
+      <c r="B119" s="69">
         <f>IFERROR(LARGE($O$3:$O$10,4),"")</f>
         <v/>
       </c>
@@ -10023,7 +10015,7 @@
         <f>IFERROR(INDEX($B$3:$B$10,MATCH(B120,$O$3:$O$10,0)),"")</f>
         <v/>
       </c>
-      <c r="B120" s="71">
+      <c r="B120" s="69">
         <f>IFERROR(LARGE($O$3:$O$10,5),"")</f>
         <v/>
       </c>
@@ -10072,7 +10064,7 @@
         <f>IFERROR(INDEX($B$3:$B$10,MATCH(B121,$O$3:$O$10,0)),"")</f>
         <v/>
       </c>
-      <c r="B121" s="71">
+      <c r="B121" s="69">
         <f>IFERROR(LARGE($O$3:$O$10,6),"")</f>
         <v/>
       </c>
@@ -10121,7 +10113,7 @@
         <f>IFERROR(INDEX($B$3:$B$10,MATCH(B122,$O$3:$O$10,0)),"")</f>
         <v/>
       </c>
-      <c r="B122" s="71">
+      <c r="B122" s="69">
         <f>IFERROR(LARGE($O$3:$O$10,7),"")</f>
         <v/>
       </c>
@@ -10170,7 +10162,7 @@
         <f>IFERROR(INDEX($B$3:$B$10,MATCH(B123,$O$3:$O$10,0)),"")</f>
         <v/>
       </c>
-      <c r="B123" s="71">
+      <c r="B123" s="69">
         <f>IFERROR(LARGE($O$3:$O$10,8),"")</f>
         <v/>
       </c>
@@ -10215,7 +10207,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="B124" s="72" t="n">
+      <c r="B124" s="70" t="n">
         <v>46268</v>
       </c>
       <c r="C124" t="inlineStr">
@@ -10259,7 +10251,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="B125" s="72" t="n">
+      <c r="B125" s="70" t="n">
         <v>46271</v>
       </c>
       <c r="C125" t="inlineStr">
@@ -10308,7 +10300,7 @@
           <t>Demo · Tendencia (6 meses)</t>
         </is>
       </c>
-      <c r="B126" s="72" t="n">
+      <c r="B126" s="70" t="n">
         <v>46272</v>
       </c>
       <c r="C126" t="inlineStr">
@@ -10356,11 +10348,11 @@
         <f>TEXT(EDATE(TODAY(),-5),"MMM")</f>
         <v/>
       </c>
-      <c r="B127" s="71">
+      <c r="B127" s="69">
         <f>SUMIFS($J$22:$J$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-5-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-5))</f>
         <v/>
       </c>
-      <c r="C127" s="71">
+      <c r="C127" s="69">
         <f>SUMIFS($L$22:$L$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-5-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-5))</f>
         <v/>
       </c>
@@ -10404,11 +10396,11 @@
         <f>TEXT(EDATE(TODAY(),-4),"MMM")</f>
         <v/>
       </c>
-      <c r="B128" s="71">
+      <c r="B128" s="69">
         <f>SUMIFS($J$22:$J$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-4-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-4))</f>
         <v/>
       </c>
-      <c r="C128" s="71">
+      <c r="C128" s="69">
         <f>SUMIFS($L$22:$L$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-4-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-4))</f>
         <v/>
       </c>
@@ -10452,11 +10444,11 @@
         <f>TEXT(EDATE(TODAY(),-3),"MMM")</f>
         <v/>
       </c>
-      <c r="B129" s="71">
+      <c r="B129" s="69">
         <f>SUMIFS($J$22:$J$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-3-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-3))</f>
         <v/>
       </c>
-      <c r="C129" s="71">
+      <c r="C129" s="69">
         <f>SUMIFS($L$22:$L$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-3-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-3))</f>
         <v/>
       </c>
@@ -10500,11 +10492,11 @@
         <f>TEXT(EDATE(TODAY(),-2),"MMM")</f>
         <v/>
       </c>
-      <c r="B130" s="71">
+      <c r="B130" s="69">
         <f>SUMIFS($J$22:$J$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-2-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-2))</f>
         <v/>
       </c>
-      <c r="C130" s="71">
+      <c r="C130" s="69">
         <f>SUMIFS($L$22:$L$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-2-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-2))</f>
         <v/>
       </c>
@@ -10548,11 +10540,11 @@
         <f>TEXT(EDATE(TODAY(),-1),"MMM")</f>
         <v/>
       </c>
-      <c r="B131" s="71">
+      <c r="B131" s="69">
         <f>SUMIFS($J$22:$J$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-1-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-1))</f>
         <v/>
       </c>
-      <c r="C131" s="71">
+      <c r="C131" s="69">
         <f>SUMIFS($L$22:$L$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-1-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-1))</f>
         <v/>
       </c>
@@ -10596,11 +10588,11 @@
         <f>TEXT(EDATE(TODAY(),-0),"MMM")</f>
         <v/>
       </c>
-      <c r="B132" s="71">
+      <c r="B132" s="69">
         <f>SUMIFS($J$22:$J$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-0-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-0))</f>
         <v/>
       </c>
-      <c r="C132" s="71">
+      <c r="C132" s="69">
         <f>SUMIFS($L$22:$L$132,$B$22:$B$132,"&gt;="&amp;EOMONTH(TODAY(),-0-1)+1,$B$22:$B$132,"&lt;="&amp;EOMONTH(TODAY(),-0))</f>
         <v/>
       </c>
@@ -10640,7 +10632,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="73" t="inlineStr">
+      <c r="A300" s="71" t="inlineStr">
         <is>
           <t>Demo · KPIs (todo el historial de 90 días)</t>
         </is>
@@ -10652,7 +10644,7 @@
           <t>Ventas del período</t>
         </is>
       </c>
-      <c r="B301" s="71">
+      <c r="B301" s="69">
         <f>SUM($J$22:$J$132)</f>
         <v/>
       </c>
@@ -10663,7 +10655,7 @@
           <t>Costos de venta del período</t>
         </is>
       </c>
-      <c r="B302" s="71">
+      <c r="B302" s="69">
         <f>SUM($K$22:$K$132)</f>
         <v/>
       </c>
@@ -10674,7 +10666,7 @@
           <t>Ganancia de productos</t>
         </is>
       </c>
-      <c r="B303" s="71">
+      <c r="B303" s="69">
         <f>B301-B302</f>
         <v/>
       </c>
@@ -10685,7 +10677,7 @@
           <t>Gastos del período</t>
         </is>
       </c>
-      <c r="B304" s="71">
+      <c r="B304" s="69">
         <f>SUM($T$4:$T$14)</f>
         <v/>
       </c>
@@ -10696,7 +10688,7 @@
           <t>Ganancia real</t>
         </is>
       </c>
-      <c r="B305" s="71">
+      <c r="B305" s="69">
         <f>B303-B304</f>
         <v/>
       </c>
@@ -10707,7 +10699,7 @@
           <t>Margen real</t>
         </is>
       </c>
-      <c r="B306" s="76">
+      <c r="B306" s="74">
         <f>IF(B301=0,0,B305/B301)</f>
         <v/>
       </c>
@@ -10718,7 +10710,7 @@
           <t>Cantidad de ventas</t>
         </is>
       </c>
-      <c r="B307" s="75">
+      <c r="B307" s="73">
         <f>COUNTA($B$22:$B$132)</f>
         <v/>
       </c>
@@ -10729,7 +10721,7 @@
           <t>Ticket promedio</t>
         </is>
       </c>
-      <c r="B308" s="71">
+      <c r="B308" s="69">
         <f>IF(B307=0,0,B301/B307)</f>
         <v/>
       </c>
@@ -10740,7 +10732,7 @@
           <t>Objetivo de ganancia</t>
         </is>
       </c>
-      <c r="B309" s="71">
+      <c r="B309" s="69">
         <f>X4</f>
         <v/>
       </c>
@@ -10751,7 +10743,7 @@
           <t>Progreso %</t>
         </is>
       </c>
-      <c r="B310" s="76">
+      <c r="B310" s="74">
         <f>IF(B309&lt;=0,0,MIN(B305/B309,1))</f>
         <v/>
       </c>
@@ -10776,12 +10768,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="70" t="inlineStr">
+      <c r="A1" s="68" t="inlineStr">
         <is>
           <t>Nombre</t>
         </is>
       </c>
-      <c r="B1" s="70" t="inlineStr">
+      <c r="B1" s="68" t="inlineStr">
         <is>
           <t>Texto</t>
         </is>
@@ -11642,7 +11634,7 @@
     <row r="11" ht="16" customHeight="1">
       <c r="B11" s="34" t="inlineStr">
         <is>
-          <t>⬜ Vos cargás esto    ·    🔸 Profitly lo completa (lo podés cambiar)    ·    🔒 Profitly lo calculó</t>
+          <t>⬜ Vos cargás esto    ·    🔒 Profitly lo calculó</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11932,7 @@
     <row r="8" ht="16" customHeight="1">
       <c r="B8" s="34" t="inlineStr">
         <is>
-          <t>⬜ Vos cargás esto    ·    🔸 Profitly lo completa (lo podés cambiar)    ·    🔒 Profitly lo calculó</t>
+          <t>⬜ Vos cargás esto    ·    🔒 Profitly lo calculó</t>
         </is>
       </c>
     </row>
@@ -12005,15 +11997,9 @@
       <c r="B10" s="45" t="n"/>
       <c r="C10" s="36" t="n"/>
       <c r="D10" s="46" t="n"/>
-      <c r="E10" s="47">
-        <f>IFERROR(INDEX(tbl_Productos[Precio de venta],MATCH(C10,tbl_Productos[Producto],0)),"")</f>
-        <v/>
-      </c>
+      <c r="E10" s="37" t="n"/>
       <c r="F10" s="36" t="n"/>
-      <c r="G10" s="48">
-        <f>IFERROR(INDEX(tbl_Productos[Comisión %],MATCH(C10,tbl_Productos[Producto],0)),"")</f>
-        <v/>
-      </c>
+      <c r="G10" s="38" t="n"/>
       <c r="H10" s="37" t="n"/>
       <c r="I10" s="37" t="n"/>
       <c r="J10" s="39">
@@ -12052,9 +12038,9 @@
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <dataValidations count="8">
-    <dataValidation sqref="E9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Precio de venta" prompt="Se completa solo cuando elegís un producto — lo podés cambiar."/>
-    <dataValidation sqref="G9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Comisión %" prompt="Se completa solo cuando elegís un producto — lo podés cambiar."/>
+  <dataValidations count="10">
+    <dataValidation sqref="E9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Precio de venta" prompt="Ingresá el precio al que vendiste — fijate el precio actual en 📦 Productos si querés usarlo de referencia."/>
+    <dataValidation sqref="G9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Comisión %" prompt="Ingresá la comisión de esta venta — fijate la comisión del producto en 📦 Productos si querés usarla de referencia."/>
     <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Producto inválido" error="Elegí un producto de tu catálogo." type="list">
       <formula1>=tbl_Productos[Producto]</formula1>
     </dataValidation>
@@ -12066,6 +12052,13 @@
     </dataValidation>
     <dataValidation sqref="D10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá una cantidad de al menos 1." type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
+    </dataValidation>
+    <dataValidation sqref="E10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="G10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá un porcentaje entre 0% y 100%." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
     </dataValidation>
     <dataValidation sqref="H10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -12374,18 +12367,18 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="49" t="n"/>
+      <c r="B7" s="47" t="n"/>
       <c r="C7" s="37">
         <f>Cfg_ObjetivoMensualDefault</f>
         <v/>
       </c>
-      <c r="F7" s="50">
+      <c r="F7" s="48">
         <f>IF(Obj_GananciaObjetivo&lt;=0,Txt_ObjetivoInvalido,TEXT(Obj_ProgresoPct,"0%")&amp;"  ·  "&amp;TEXT(Obj_GananciaActual,Cfg_Moneda&amp;"#,##0")&amp;" de "&amp;TEXT(Obj_GananciaObjetivo,Cfg_Moneda&amp;"#,##0"))</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="51">
+      <c r="B9" s="49">
         <f>IF(AND(Cfg_ObjetivoMensualDefault=0,COUNTA(tbl_Objetivos[Objetivo de ganancia])&lt;=1),"Todavía no definiste un objetivo. ¿Cuánto querés ganar este mes?","")</f>
         <v/>
       </c>
@@ -12394,7 +12387,7 @@
           <t>Ganancia objetivo</t>
         </is>
       </c>
-      <c r="H9" s="52">
+      <c r="H9" s="50">
         <f>Obj_GananciaObjetivo</f>
         <v/>
       </c>
@@ -12405,7 +12398,7 @@
           <t>Ganancia actual</t>
         </is>
       </c>
-      <c r="H10" s="52">
+      <c r="H10" s="50">
         <f>Obj_GananciaActual</f>
         <v/>
       </c>
@@ -12416,7 +12409,7 @@
           <t>Restante</t>
         </is>
       </c>
-      <c r="H11" s="52">
+      <c r="H11" s="50">
         <f>Obj_Restante</f>
         <v/>
       </c>
@@ -12427,7 +12420,7 @@
           <t>Ganancia diaria necesaria</t>
         </is>
       </c>
-      <c r="H12" s="52">
+      <c r="H12" s="50">
         <f>Obj_GananciaDiariaNecesaria</f>
         <v/>
       </c>
@@ -12438,7 +12431,7 @@
           <t>Facturación necesaria</t>
         </is>
       </c>
-      <c r="H13" s="52">
+      <c r="H13" s="50">
         <f>Obj_FacturacionNecesaria</f>
         <v/>
       </c>
@@ -12449,13 +12442,13 @@
           <t>Ventas necesarias</t>
         </is>
       </c>
-      <c r="H14" s="53">
+      <c r="H14" s="51">
         <f>Obj_VentasNecesarias</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="F16" s="54">
+      <c r="F16" s="52">
         <f>Obj_Factibilidad</f>
         <v/>
       </c>
@@ -12598,7 +12591,7 @@
     </row>
     <row r="5" ht="6" customHeight="1"/>
     <row r="6">
-      <c r="B6" s="55">
+      <c r="B6" s="53">
         <f>IF(NOT(Sim_DatosSuficientes),"Necesitás cargar ventas reales antes de simular escenarios. → Ir a 🛒 Ventas","")</f>
         <v/>
       </c>
@@ -12611,440 +12604,440 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="56" t="inlineStr">
+      <c r="B8" s="54" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
-      <c r="D8" s="57">
+      <c r="D8" s="55">
         <f>Sim_Base_Ventas</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="56" t="inlineStr">
+      <c r="B9" s="54" t="inlineStr">
         <is>
           <t>Costos de venta</t>
         </is>
       </c>
-      <c r="D9" s="57">
+      <c r="D9" s="55">
         <f>Sim_Base_CostosVenta</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="56" t="inlineStr">
+      <c r="B10" s="54" t="inlineStr">
         <is>
           <t>Ganancia de productos</t>
         </is>
       </c>
-      <c r="D10" s="57">
+      <c r="D10" s="55">
         <f>Sim_Base_GananciaProductos</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="56" t="inlineStr">
+      <c r="B11" s="54" t="inlineStr">
         <is>
           <t>Gastos</t>
         </is>
       </c>
-      <c r="D11" s="57">
+      <c r="D11" s="55">
         <f>Sim_Base_Gastos</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="56" t="inlineStr">
+      <c r="B12" s="54" t="inlineStr">
         <is>
           <t>Ganancia real</t>
         </is>
       </c>
-      <c r="D12" s="57">
+      <c r="D12" s="55">
         <f>Sim_Base_GananciaReal</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="56" t="inlineStr">
+      <c r="B13" s="54" t="inlineStr">
         <is>
           <t>Margen</t>
         </is>
       </c>
-      <c r="D13" s="58">
+      <c r="D13" s="56">
         <f>Sim_Base_Margen</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="59" t="inlineStr">
+      <c r="B15" s="57" t="inlineStr">
         <is>
           <t>Escenario A</t>
         </is>
       </c>
-      <c r="F15" s="59" t="inlineStr">
+      <c r="F15" s="57" t="inlineStr">
         <is>
           <t>Escenario B</t>
         </is>
       </c>
-      <c r="J15" s="59" t="inlineStr">
+      <c r="J15" s="57" t="inlineStr">
         <is>
           <t>Escenario C</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="60" t="inlineStr">
+      <c r="B16" s="58" t="inlineStr">
         <is>
           <t>Δ Precio %</t>
         </is>
       </c>
-      <c r="D16" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="60" t="inlineStr">
+      <c r="D16" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="58" t="inlineStr">
         <is>
           <t>Δ Precio %</t>
         </is>
       </c>
-      <c r="H16" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="60" t="inlineStr">
+      <c r="H16" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="58" t="inlineStr">
         <is>
           <t>Δ Precio %</t>
         </is>
       </c>
-      <c r="L16" s="61" t="n">
+      <c r="L16" s="59" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="60" t="inlineStr">
+      <c r="B17" s="58" t="inlineStr">
         <is>
           <t>Δ Cantidad de ventas %</t>
         </is>
       </c>
-      <c r="D17" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="60" t="inlineStr">
+      <c r="D17" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="58" t="inlineStr">
         <is>
           <t>Δ Cantidad de ventas %</t>
         </is>
       </c>
-      <c r="H17" s="61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="60" t="inlineStr">
+      <c r="H17" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="58" t="inlineStr">
         <is>
           <t>Δ Cantidad de ventas %</t>
         </is>
       </c>
-      <c r="L17" s="61" t="n">
+      <c r="L17" s="59" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="60" t="inlineStr">
+      <c r="B18" s="58" t="inlineStr">
         <is>
           <t>Δ Margen (pp)</t>
         </is>
       </c>
-      <c r="D18" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="60" t="inlineStr">
+      <c r="D18" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="58" t="inlineStr">
         <is>
           <t>Δ Margen (pp)</t>
         </is>
       </c>
-      <c r="H18" s="62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="60" t="inlineStr">
+      <c r="H18" s="60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="58" t="inlineStr">
         <is>
           <t>Δ Margen (pp)</t>
         </is>
       </c>
-      <c r="L18" s="62" t="n">
+      <c r="L18" s="60" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="60" t="inlineStr">
+      <c r="B19" s="58" t="inlineStr">
         <is>
           <t>Δ Gastos ($)</t>
         </is>
       </c>
-      <c r="D19" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="60" t="inlineStr">
+      <c r="D19" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="58" t="inlineStr">
         <is>
           <t>Δ Gastos ($)</t>
         </is>
       </c>
-      <c r="H19" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="60" t="inlineStr">
+      <c r="H19" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="58" t="inlineStr">
         <is>
           <t>Δ Gastos ($)</t>
         </is>
       </c>
-      <c r="L19" s="63" t="n">
+      <c r="L19" s="61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="60" t="inlineStr">
+      <c r="B20" s="58" t="inlineStr">
         <is>
           <t>Δ Publicidad ($)</t>
         </is>
       </c>
-      <c r="D20" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="60" t="inlineStr">
+      <c r="D20" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="58" t="inlineStr">
         <is>
           <t>Δ Publicidad ($)</t>
         </is>
       </c>
-      <c r="H20" s="63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="60" t="inlineStr">
+      <c r="H20" s="61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="58" t="inlineStr">
         <is>
           <t>Δ Publicidad ($)</t>
         </is>
       </c>
-      <c r="L20" s="63" t="n">
+      <c r="L20" s="61" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="64" t="inlineStr">
+      <c r="B22" s="62" t="inlineStr">
         <is>
           <t>ESCENARIO PROYECTADO</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="60" t="inlineStr">
+      <c r="B23" s="58" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
-      <c r="D23" s="57">
+      <c r="D23" s="55">
         <f>Sim_A_VentasProyectadas</f>
         <v/>
       </c>
-      <c r="F23" s="60" t="inlineStr">
+      <c r="F23" s="58" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
-      <c r="H23" s="57">
+      <c r="H23" s="55">
         <f>Sim_B_VentasProyectadas</f>
         <v/>
       </c>
-      <c r="J23" s="60" t="inlineStr">
+      <c r="J23" s="58" t="inlineStr">
         <is>
           <t>Ventas</t>
         </is>
       </c>
-      <c r="L23" s="57">
+      <c r="L23" s="55">
         <f>Sim_C_VentasProyectadas</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="60" t="inlineStr">
+      <c r="B24" s="58" t="inlineStr">
         <is>
           <t>Costos de venta</t>
         </is>
       </c>
-      <c r="D24" s="57">
+      <c r="D24" s="55">
         <f>Sim_A_CostosVentaProyectados</f>
         <v/>
       </c>
-      <c r="F24" s="60" t="inlineStr">
+      <c r="F24" s="58" t="inlineStr">
         <is>
           <t>Costos de venta</t>
         </is>
       </c>
-      <c r="H24" s="57">
+      <c r="H24" s="55">
         <f>Sim_B_CostosVentaProyectados</f>
         <v/>
       </c>
-      <c r="J24" s="60" t="inlineStr">
+      <c r="J24" s="58" t="inlineStr">
         <is>
           <t>Costos de venta</t>
         </is>
       </c>
-      <c r="L24" s="57">
+      <c r="L24" s="55">
         <f>Sim_C_CostosVentaProyectados</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="60" t="inlineStr">
+      <c r="B25" s="58" t="inlineStr">
         <is>
           <t>Ganancia de productos</t>
         </is>
       </c>
-      <c r="D25" s="57">
+      <c r="D25" s="55">
         <f>Sim_A_GananciaProductosProyectada</f>
         <v/>
       </c>
-      <c r="F25" s="60" t="inlineStr">
+      <c r="F25" s="58" t="inlineStr">
         <is>
           <t>Ganancia de productos</t>
         </is>
       </c>
-      <c r="H25" s="57">
+      <c r="H25" s="55">
         <f>Sim_B_GananciaProductosProyectada</f>
         <v/>
       </c>
-      <c r="J25" s="60" t="inlineStr">
+      <c r="J25" s="58" t="inlineStr">
         <is>
           <t>Ganancia de productos</t>
         </is>
       </c>
-      <c r="L25" s="57">
+      <c r="L25" s="55">
         <f>Sim_C_GananciaProductosProyectada</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="60" t="inlineStr">
+      <c r="B26" s="58" t="inlineStr">
         <is>
           <t>Gastos</t>
         </is>
       </c>
-      <c r="D26" s="57">
+      <c r="D26" s="55">
         <f>Sim_A_GastosProyectados</f>
         <v/>
       </c>
-      <c r="F26" s="60" t="inlineStr">
+      <c r="F26" s="58" t="inlineStr">
         <is>
           <t>Gastos</t>
         </is>
       </c>
-      <c r="H26" s="57">
+      <c r="H26" s="55">
         <f>Sim_B_GastosProyectados</f>
         <v/>
       </c>
-      <c r="J26" s="60" t="inlineStr">
+      <c r="J26" s="58" t="inlineStr">
         <is>
           <t>Gastos</t>
         </is>
       </c>
-      <c r="L26" s="57">
+      <c r="L26" s="55">
         <f>Sim_C_GastosProyectados</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="60" t="inlineStr">
+      <c r="B27" s="58" t="inlineStr">
         <is>
           <t>Ganancia real</t>
         </is>
       </c>
-      <c r="D27" s="57">
+      <c r="D27" s="55">
         <f>Sim_A_GananciaRealProyectada</f>
         <v/>
       </c>
-      <c r="F27" s="60" t="inlineStr">
+      <c r="F27" s="58" t="inlineStr">
         <is>
           <t>Ganancia real</t>
         </is>
       </c>
-      <c r="H27" s="57">
+      <c r="H27" s="55">
         <f>Sim_B_GananciaRealProyectada</f>
         <v/>
       </c>
-      <c r="J27" s="60" t="inlineStr">
+      <c r="J27" s="58" t="inlineStr">
         <is>
           <t>Ganancia real</t>
         </is>
       </c>
-      <c r="L27" s="57">
+      <c r="L27" s="55">
         <f>Sim_C_GananciaRealProyectada</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="60" t="inlineStr">
+      <c r="B28" s="58" t="inlineStr">
         <is>
           <t>Margen</t>
         </is>
       </c>
-      <c r="D28" s="58">
+      <c r="D28" s="56">
         <f>Sim_A_MargenProyectado</f>
         <v/>
       </c>
-      <c r="F28" s="60" t="inlineStr">
+      <c r="F28" s="58" t="inlineStr">
         <is>
           <t>Margen</t>
         </is>
       </c>
-      <c r="H28" s="58">
+      <c r="H28" s="56">
         <f>Sim_B_MargenProyectado</f>
         <v/>
       </c>
-      <c r="J28" s="60" t="inlineStr">
+      <c r="J28" s="58" t="inlineStr">
         <is>
           <t>Margen</t>
         </is>
       </c>
-      <c r="L28" s="58">
+      <c r="L28" s="56">
         <f>Sim_C_MargenProyectado</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="65" t="inlineStr">
+      <c r="B29" s="63" t="inlineStr">
         <is>
           <t>DIFERENCIA</t>
         </is>
       </c>
-      <c r="F29" s="65" t="inlineStr">
+      <c r="F29" s="63" t="inlineStr">
         <is>
           <t>DIFERENCIA</t>
         </is>
       </c>
-      <c r="J29" s="65" t="inlineStr">
+      <c r="J29" s="63" t="inlineStr">
         <is>
           <t>DIFERENCIA</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="66">
+      <c r="B30" s="64">
         <f>Sim_A_Diferencia</f>
         <v/>
       </c>
-      <c r="F30" s="66">
+      <c r="F30" s="64">
         <f>Sim_B_Diferencia</f>
         <v/>
       </c>
-      <c r="J30" s="66">
+      <c r="J30" s="64">
         <f>Sim_C_Diferencia</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="67">
+      <c r="B31" s="65">
         <f>IF(Sim_A_GastosAjustados=TRUE,"Ajustamos tus gastos proyectados a $0 porque el valor ingresado los volvía negativos.","")</f>
         <v/>
       </c>
-      <c r="F31" s="67">
+      <c r="F31" s="65">
         <f>IF(Sim_B_GastosAjustados=TRUE,"Ajustamos tus gastos proyectados a $0 porque el valor ingresado los volvía negativos.","")</f>
         <v/>
       </c>
-      <c r="J31" s="67">
+      <c r="J31" s="65">
         <f>IF(Sim_C_GastosAjustados=TRUE,"Ajustamos tus gastos proyectados a $0 porque el valor ingresado los volvía negativos.","")</f>
         <v/>
       </c>
@@ -13210,7 +13203,7 @@
           <t>🔬 Simulador</t>
         </is>
       </c>
-      <c r="Q1" s="68">
+      <c r="Q1" s="66">
         <f>"🎬 DEMO"</f>
         <v/>
       </c>
@@ -13232,7 +13225,7 @@
     </row>
     <row r="5" ht="6" customHeight="1"/>
     <row r="6">
-      <c r="B6" s="69" t="inlineStr">
+      <c r="B6" s="67" t="inlineStr">
         <is>
           <t>Estás viendo datos de ejemplo. Cuando quieras, pasá a 🚀 Mi Negocio para cargar los tuyos.</t>
         </is>

--- a/build/Profitly.xlsx
+++ b/build/Profitly.xlsx
@@ -41,14 +41,12 @@
     <definedName name="Cfg_NombreNegocio">'⚙️ Configuración'!$C$11</definedName>
     <definedName name="Cfg_TipoNegocio">'⚙️ Configuración'!$C$12</definedName>
     <definedName name="Cfg_Moneda">'⚙️ Configuración'!$C$13</definedName>
-    <definedName name="Cfg_ObjetivoMensualDefault">'⚙️ Configuración'!$C$24</definedName>
+    <definedName name="Cfg_ObjetivoMensualDefault">'⚙️ Configuración'!$C$35</definedName>
     <definedName name="Cfg_PeriodoInicio">_Config!$B$6</definedName>
     <definedName name="Cfg_PeriodoFin">_Config!$B$7</definedName>
     <definedName name="Cfg_MargenAlertaUmbral">_Config!$B$8</definedName>
     <definedName name="Cfg_PeriodoInicio_Ant">_Config!$B$10</definedName>
     <definedName name="Cfg_PeriodoFin_Ant">_Config!$B$11</definedName>
-    <definedName name="Lst_Categorias">_Listas!$A$2:$A$8</definedName>
-    <definedName name="Lst_Canales">_Listas!$B$2:$B$6</definedName>
     <definedName name="Lst_CategoriasGasto">_Listas!$C$2:$C$7</definedName>
     <definedName name="Lst_TiposGasto">_Listas!$D$2:$D$4</definedName>
     <definedName name="Lst_Monedas">_Listas!$E$2:$E$6</definedName>
@@ -169,6 +167,8 @@
     <definedName name="DemoKPI_ProgresoPct">_Demo_Datos!$B$310</definedName>
     <definedName name="Demo_ProductoRankRange">_Demo_Datos!$A$116:$B$123</definedName>
     <definedName name="Demo_TrendRange">_Demo_Datos!$A$127:$C$132</definedName>
+    <definedName name="Lst_Categorias">'⚙️ Configuración'!$C$16:$C$23</definedName>
+    <definedName name="Lst_Canales">'⚙️ Configuración'!$C$25:$C$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -176,14 +176,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.0%;[RED]-0.0%;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="$#,##0;[RED]-$#,##0;&quot;-&quot;"/>
-    <numFmt numFmtId="166" formatCode="DD/MM/YYYY"/>
-    <numFmt numFmtId="167" formatCode="MMMM YYYY"/>
-    <numFmt numFmtId="168" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="+$#,##0;-$#,##0;&quot;-&quot;"/>
-    <numFmt numFmtId="170" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="[=1]&quot;⚠️&quot;;;"/>
+    <numFmt numFmtId="167" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="168" formatCode="MMMM YYYY"/>
+    <numFmt numFmtId="169" formatCode="0.0"/>
+    <numFmt numFmtId="170" formatCode="+$#,##0;-$#,##0;&quot;-&quot;"/>
+    <numFmt numFmtId="171" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="35">
     <font>
@@ -708,14 +709,14 @@
     <xf numFmtId="3" fontId="12" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="12" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="12" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -723,7 +724,7 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="167" fontId="12" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="12" fillId="4" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -758,7 +759,7 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="168" fontId="1" fillId="8" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="1" fillId="8" borderId="8" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -770,7 +771,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="19" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="19" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -784,7 +785,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -922,7 +923,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln w="24000">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -955,7 +959,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln w="24000">
+              <a:solidFill>
+                <a:srgbClr val="1E8E5A"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1046,6 +1053,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1E3A5F"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1126,6 +1136,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1E8E5A"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1145,6 +1158,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E8EAED"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1223,7 +1239,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln w="24000">
+              <a:solidFill>
+                <a:srgbClr val="6B7280"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1256,7 +1275,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln w="24000">
+              <a:solidFill>
+                <a:srgbClr val="1E8E5A"/>
+              </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -1347,6 +1369,9 @@
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1E3A5F"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -1423,17 +1448,20 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_Demo_Datos'!R115</f>
+              <f>'_Demo_Datos'!Z312</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1E8E5A"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <val>
             <numRef>
-              <f>'_Demo_Datos'!$R$116</f>
+              <f>'_Demo_Datos'!$Z$313</f>
             </numRef>
           </val>
         </ser>
@@ -1442,17 +1470,20 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'_Demo_Datos'!S115</f>
+              <f>'_Demo_Datos'!AA312</f>
             </strRef>
           </tx>
           <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E8EAED"/>
+            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <val>
             <numRef>
-              <f>'_Demo_Datos'!$S$116</f>
+              <f>'_Demo_Datos'!$AA$313</f>
             </numRef>
           </val>
         </ser>
@@ -1990,6 +2021,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2166,11 +2198,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="C1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
@@ -2178,16 +2208,6 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="68" t="inlineStr">
-        <is>
-          <t>Lst_Categorias</t>
-        </is>
-      </c>
-      <c r="B1" s="68" t="inlineStr">
-        <is>
-          <t>Lst_Canales</t>
-        </is>
-      </c>
       <c r="C1" s="68" t="inlineStr">
         <is>
           <t>Lst_CategoriasGasto</t>
@@ -2210,16 +2230,6 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Local</t>
-        </is>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Publicidad</t>
@@ -2242,16 +2252,6 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Alimentos</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Software/Suscripciones</t>
@@ -2274,16 +2274,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Indumentaria</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Mayorista</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Internet</t>
@@ -2306,16 +2296,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Accesorios</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Redes sociales</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Packaging general</t>
@@ -2333,16 +2313,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Hogar</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Feria</t>
-        </is>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Herramientas</t>
@@ -2355,21 +2325,9 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Belleza</t>
-        </is>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>Otros</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Servicios</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X310"/>
+  <dimension ref="A1:AA313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10745,6 +10703,28 @@
       </c>
       <c r="B310" s="74">
         <f>IF(B309&lt;=0,0,MIN(B305/B309,1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312">
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t>Alcanzado</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>Restante</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="Z313">
+        <f>DemoKPI_GananciaReal</f>
+        <v/>
+      </c>
+      <c r="AA313">
+        <f>MAX(DemoKPI_Objetivo-DemoKPI_GananciaReal,0)</f>
         <v/>
       </c>
     </row>
@@ -10908,6 +10888,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -10991,7 +10972,7 @@
     <row r="5" ht="6" customHeight="1"/>
     <row r="6">
       <c r="B6" s="11">
-        <f>IF(COUNTA(tbl_Productos[Producto])=0,"🚀 Te falta 1 paso para ver tu panorama completo: Configurá tu negocio y agregá productos → Ir a ⚙️ Configuración",IF(COUNTA(tbl_Ventas[Fecha])=0,"🚀 Te falta 1 paso: Registrá tu primera venta → Ir a 🛒 Ventas",IF(COUNTA(tbl_Gastos[Fecha])=0,"🚀 Te falta 1 paso: Registrá tus gastos → Ir a 💸 Gastos",IF(OR(Cfg_ObjetivoMensualDefault=0,COUNTA(tbl_Objetivos[Objetivo de ganancia])&lt;=1),"🚀 Te falta 1 paso: Definí tu objetivo mensual → Ir a 🎯 Objetivos",""))))</f>
+        <f>IF(NOT(OR(COUNTA(tbl_Productos[Producto])=0,COUNTA(tbl_Ventas[Fecha])=0,COUNTA(tbl_Gastos[Fecha])=0,AND(Cfg_ObjetivoMensualDefault=0,COUNTA(tbl_Objetivos[Objetivo de ganancia])&lt;=1))),"",HYPERLINK("#'"&amp;IF(COUNTA(tbl_Productos[Producto])=0,"⚙️ Configuración",IF(COUNTA(tbl_Ventas[Fecha])=0,"🛒 Ventas",IF(COUNTA(tbl_Gastos[Fecha])=0,"💸 Gastos","🎯 Objetivos")))&amp;"'!A1",IF(COUNTA(tbl_Productos[Producto])=0,"🚀 Te falta 1 paso para ver tu panorama completo: Configurá tu negocio y agregá productos → Ir a ⚙️ Configuración",IF(COUNTA(tbl_Ventas[Fecha])=0,"🚀 Te falta 1 paso: Registrá tu primera venta → Ir a 🛒 Ventas",IF(COUNTA(tbl_Gastos[Fecha])=0,"🚀 Te falta 1 paso: Registrá tus gastos → Ir a 💸 Gastos","🚀 Te falta 1 paso: Definí tu objetivo mensual → Ir a 🎯 Objetivos")))))</f>
         <v/>
       </c>
     </row>
@@ -11007,7 +10988,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="16" customHeight="1">
       <c r="B9" s="14" t="inlineStr">
         <is>
           <t>VENTAS</t>
@@ -11029,7 +11010,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="B10" s="15">
         <f>KPI_VentasPeriodo</f>
         <v/>
@@ -11047,7 +11028,7 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14" customHeight="1">
       <c r="B11" s="17">
         <f>IF(KPI_VentasPeriodo_Delta="","",IF(KPI_VentasPeriodo_Delta&gt;0,"▲ ","▼ ")&amp;TEXT(ABS(KPI_VentasPeriodo_Delta),"0%")&amp;" vs. período anterior")</f>
         <v/>
@@ -11065,7 +11046,7 @@
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="16" customHeight="1">
       <c r="B13" s="14" t="inlineStr">
         <is>
           <t>TICKET PROMEDIO</t>
@@ -11082,7 +11063,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="B14" s="15">
         <f>KPI_TicketPromedio</f>
         <v/>
@@ -11096,7 +11077,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="18" t="inlineStr"/>
       <c r="F15" s="18" t="inlineStr"/>
       <c r="J15" s="18" t="inlineStr"/>
@@ -11203,10 +11184,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:S26"/>
+  <dimension ref="B1:S37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -11382,50 +11364,131 @@
     <row r="16">
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>(Se cargan en 📦 Productos como lista desplegable — editá la lista base en la hoja _Listas.)</t>
+          <t>Agregá o cambiá las categorías que ves como opciones en 📦 Productos.</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>Alimentos</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="19" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>Indumentaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>Accesorios</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>Hogar</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>Belleza</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" s="24" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Canales de venta</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>(Se cargan en 🛒 Ventas como lista desplegable — editá la lista base en la hoja _Listas.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="26" t="inlineStr">
+    <row r="25">
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>Mayorista</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>Redes sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>Feria</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="24" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>💡 Cargá tus gastos fijos (alquiler, herramientas, suscripciones) en 💸 Gastos para que tu Ganancia real sea precisa.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="19" t="inlineStr">
+    <row r="34">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>Objetivo mensual</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="23" t="inlineStr">
+    <row r="35">
+      <c r="B35" s="23" t="inlineStr">
         <is>
           <t>¿Cuánto querés ganar por mes?</t>
         </is>
       </c>
-      <c r="C24" s="27" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="28" t="inlineStr">
+      <c r="C35" s="27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>No hay botón "Guardar" — todo se guarda automáticamente a medida que escribís, como en cualquier planilla.</t>
         </is>
@@ -11441,13 +11504,14 @@
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="Q1:S1"/>
     <mergeCell ref="H6:I6"/>
+    <mergeCell ref="B37:P37"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="N1:O1"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="H7:I7"/>
     <mergeCell ref="L1:M1"/>
+    <mergeCell ref="B32:P32"/>
     <mergeCell ref="B4:P4"/>
-    <mergeCell ref="B26:P26"/>
     <mergeCell ref="B6:C6"/>
     <mergeCell ref="K7:L7"/>
     <mergeCell ref="E7:F7"/>
@@ -11455,13 +11519,12 @@
     <mergeCell ref="B3:P3"/>
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="B21:P21"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Lst_Monedas</formula1>
     </dataValidation>
-    <dataValidation sqref="C24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+    <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
@@ -11476,7 +11539,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11485,6 +11548,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -11784,10 +11848,13 @@
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="F1:G1"/>
   </mergeCells>
-  <dataValidations count="11">
+  <dataValidations count="12">
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Más rentable" prompt="El producto con mejor margen entre los que ya vendiste."/>
     <dataValidation sqref="F7" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Más vendido" prompt="El producto que más unidades vendiste. No es necesariamente el que más ganancia te deja — mirá &quot;Más rentable&quot; para eso."/>
     <dataValidation sqref="F12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Comisión %" prompt="Se completa solo cuando elegís un producto — lo podés cambiar."/>
+    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una categoría de la lista." type="list">
+      <formula1>=Lst_Categorias</formula1>
+    </dataValidation>
     <dataValidation sqref="D13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
@@ -11832,6 +11899,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -12086,6 +12154,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -12268,6 +12337,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -12509,6 +12579,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E3A5F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -12520,13 +12591,13 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col hidden="1" outlineLevel="1" width="15" customWidth="1" min="6" max="12"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
+    <col hidden="1" outlineLevel="1" width="15" customWidth="1" min="6" max="6"/>
+    <col hidden="1" outlineLevel="1" width="15" customWidth="1" min="7" max="7"/>
+    <col hidden="1" outlineLevel="1" width="15" customWidth="1" min="8" max="8"/>
+    <col hidden="1" outlineLevel="1" width="15" customWidth="1" min="9" max="9"/>
+    <col hidden="1" outlineLevel="1" width="15" customWidth="1" min="10" max="10"/>
+    <col hidden="1" outlineLevel="1" width="15" customWidth="1" min="11" max="11"/>
+    <col hidden="1" outlineLevel="1" width="15" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -13077,17 +13148,17 @@
   <dataValidations count="24">
     <dataValidation sqref="B16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Precio %" prompt="Cuánto cambiarías tu precio de venta."/>
     <dataValidation sqref="B17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Cantidad de ventas %" prompt="Cuánto cambiaría la cantidad de unidades que vendés."/>
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Margen" prompt="Este ajuste se suma al efecto que ya tiene un cambio de precio sobre tu margen."/>
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Margen" prompt="pp = puntos porcentuales (ej.: de 20% a 25% es +5 pp). Este ajuste se suma al efecto que ya tiene un cambio de precio sobre tu margen."/>
     <dataValidation sqref="B19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Gastos" prompt="Cambio en tus gastos generales del negocio."/>
     <dataValidation sqref="B20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Publicidad" prompt="Gasto adicional en publicidad para este escenario."/>
     <dataValidation sqref="F16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Precio %" prompt="Cuánto cambiarías tu precio de venta."/>
     <dataValidation sqref="F17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Cantidad de ventas %" prompt="Cuánto cambiaría la cantidad de unidades que vendés."/>
-    <dataValidation sqref="F18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Margen" prompt="Este ajuste se suma al efecto que ya tiene un cambio de precio sobre tu margen."/>
+    <dataValidation sqref="F18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Margen" prompt="pp = puntos porcentuales (ej.: de 20% a 25% es +5 pp). Este ajuste se suma al efecto que ya tiene un cambio de precio sobre tu margen."/>
     <dataValidation sqref="F19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Gastos" prompt="Cambio en tus gastos generales del negocio."/>
     <dataValidation sqref="F20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Publicidad" prompt="Gasto adicional en publicidad para este escenario."/>
     <dataValidation sqref="J16" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Precio %" prompt="Cuánto cambiarías tu precio de venta."/>
     <dataValidation sqref="J17" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Cantidad de ventas %" prompt="Cuánto cambiaría la cantidad de unidades que vendés."/>
-    <dataValidation sqref="J18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Margen" prompt="Este ajuste se suma al efecto que ya tiene un cambio de precio sobre tu margen."/>
+    <dataValidation sqref="J18" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Margen" prompt="pp = puntos porcentuales (ej.: de 20% a 25% es +5 pp). Este ajuste se suma al efecto que ya tiene un cambio de precio sobre tu margen."/>
     <dataValidation sqref="J19" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Gastos" prompt="Cambio en tus gastos generales del negocio."/>
     <dataValidation sqref="J20" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Δ Publicidad" prompt="Gasto adicional en publicidad para este escenario."/>
     <dataValidation sqref="D16" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá un porcentaje razonable." type="decimal" operator="between">
@@ -13143,10 +13214,11 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00B7791F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:S116"/>
+  <dimension ref="B1:S19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.5" customWidth="1" min="1" max="1"/>
@@ -13231,7 +13303,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="16" customHeight="1">
       <c r="B9" s="14" t="inlineStr">
         <is>
           <t>VENTAS</t>
@@ -13253,7 +13325,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="24" customHeight="1">
       <c r="B10" s="15">
         <f>DemoKPI_VentasPeriodo</f>
         <v/>
@@ -13271,13 +13343,13 @@
         <v/>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="14" customHeight="1">
       <c r="B11" s="18" t="inlineStr"/>
       <c r="F11" s="18" t="inlineStr"/>
       <c r="J11" s="18" t="inlineStr"/>
       <c r="N11" s="18" t="inlineStr"/>
     </row>
-    <row r="13">
+    <row r="13" ht="16" customHeight="1">
       <c r="B13" s="14" t="inlineStr">
         <is>
           <t>TICKET PROMEDIO</t>
@@ -13294,7 +13366,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="24" customHeight="1">
       <c r="B14" s="15">
         <f>DemoKPI_TicketPromedio</f>
         <v/>
@@ -13308,7 +13380,7 @@
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="14" customHeight="1">
       <c r="B15" s="18" t="inlineStr"/>
       <c r="F15" s="18" t="inlineStr"/>
       <c r="J15" s="18" t="inlineStr"/>
@@ -13332,28 +13404,6 @@
         <is>
           <t>🎯 Te faltan $45.000 de ganancia para alcanzar tu objetivo.</t>
         </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>Alcanzado</t>
-        </is>
-      </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>Restante</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="R116">
-        <f>DemoKPI_GananciaReal</f>
-        <v/>
-      </c>
-      <c r="S116">
-        <f>MAX(DemoKPI_Objetivo-DemoKPI_GananciaReal,0)</f>
-        <v/>
       </c>
     </row>
   </sheetData>

--- a/build/Profitly.xlsx
+++ b/build/Profitly.xlsx
@@ -2100,8 +2100,8 @@
     <mergeCell ref="I9:M14"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId2"/>
+    <hyperlink ref="C9" location="'🎬 Demo'!A1"/>
+    <hyperlink ref="I9" location="'🏠 Inicio'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11169,15 +11169,15 @@
     <dataValidation sqref="J9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="MARGEN" prompt="Porcentaje de tus ventas que queda después de descontar los costos asociados a vender."/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId6"/>
+    <hyperlink ref="D1" location="'⚙️ Configuración'!A1"/>
+    <hyperlink ref="F1" location="'📦 Productos'!A1"/>
+    <hyperlink ref="H1" location="'🛒 Ventas'!A1"/>
+    <hyperlink ref="J1" location="'💸 Gastos'!A1"/>
+    <hyperlink ref="L1" location="'🎯 Objetivos'!A1"/>
+    <hyperlink ref="N1" location="'🔬 Simulador'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11529,17 +11529,17 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId11"/>
+    <hyperlink ref="B1" location="'🏠 Inicio'!A1"/>
+    <hyperlink ref="F1" location="'📦 Productos'!A1"/>
+    <hyperlink ref="H1" location="'🛒 Ventas'!A1"/>
+    <hyperlink ref="J1" location="'💸 Gastos'!A1"/>
+    <hyperlink ref="L1" location="'🎯 Objetivos'!A1"/>
+    <hyperlink ref="N1" location="'🔬 Simulador'!A1"/>
+    <hyperlink ref="E6" location="'📦 Productos'!A1"/>
+    <hyperlink ref="H6" location="'🛒 Ventas'!A1"/>
+    <hyperlink ref="K6" location="'💸 Gastos'!A1"/>
+    <hyperlink ref="N6" location="'🏠 Inicio'!A1"/>
+    <hyperlink ref="B32" location="'💸 Gastos'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11882,16 +11882,16 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId6"/>
+    <hyperlink ref="B1" location="'🏠 Inicio'!A1"/>
+    <hyperlink ref="D1" location="'⚙️ Configuración'!A1"/>
+    <hyperlink ref="H1" location="'🛒 Ventas'!A1"/>
+    <hyperlink ref="J1" location="'💸 Gastos'!A1"/>
+    <hyperlink ref="L1" location="'🎯 Objetivos'!A1"/>
+    <hyperlink ref="N1" location="'🔬 Simulador'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12136,17 +12136,17 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId7"/>
+    <hyperlink ref="B1" location="'🏠 Inicio'!A1"/>
+    <hyperlink ref="D1" location="'⚙️ Configuración'!A1"/>
+    <hyperlink ref="F1" location="'📦 Productos'!A1"/>
+    <hyperlink ref="J1" location="'💸 Gastos'!A1"/>
+    <hyperlink ref="L1" location="'🎯 Objetivos'!A1"/>
+    <hyperlink ref="N1" location="'🔬 Simulador'!A1"/>
+    <hyperlink ref="B7" location="'📦 Productos'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12320,16 +12320,16 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId6"/>
+    <hyperlink ref="B1" location="'🏠 Inicio'!A1"/>
+    <hyperlink ref="D1" location="'⚙️ Configuración'!A1"/>
+    <hyperlink ref="F1" location="'📦 Productos'!A1"/>
+    <hyperlink ref="H1" location="'🛒 Ventas'!A1"/>
+    <hyperlink ref="L1" location="'🎯 Objetivos'!A1"/>
+    <hyperlink ref="N1" location="'🔬 Simulador'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12562,16 +12562,16 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId6"/>
+    <hyperlink ref="B1" location="'🏠 Inicio'!A1"/>
+    <hyperlink ref="D1" location="'⚙️ Configuración'!A1"/>
+    <hyperlink ref="F1" location="'📦 Productos'!A1"/>
+    <hyperlink ref="H1" location="'🛒 Ventas'!A1"/>
+    <hyperlink ref="J1" location="'💸 Gastos'!A1"/>
+    <hyperlink ref="N1" location="'🔬 Simulador'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -13199,13 +13199,13 @@
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId7"/>
+    <hyperlink ref="B1" location="'🏠 Inicio'!A1"/>
+    <hyperlink ref="D1" location="'⚙️ Configuración'!A1"/>
+    <hyperlink ref="F1" location="'📦 Productos'!A1"/>
+    <hyperlink ref="H1" location="'🛒 Ventas'!A1"/>
+    <hyperlink ref="J1" location="'💸 Gastos'!A1"/>
+    <hyperlink ref="L1" location="'🎯 Objetivos'!A1"/>
+    <hyperlink ref="B6" location="'🛒 Ventas'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13458,16 +13458,16 @@
     <dataValidation sqref="J9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="MARGEN" prompt="Porcentaje de tus ventas que queda después de descontar los costos asociados a vender."/>
   </dataValidations>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D1" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F1" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H1" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J1" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L1" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N1" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId8"/>
+    <hyperlink ref="B1" location="'🏠 Inicio'!A1"/>
+    <hyperlink ref="D1" location="'⚙️ Configuración'!A1"/>
+    <hyperlink ref="F1" location="'📦 Productos'!A1"/>
+    <hyperlink ref="H1" location="'🛒 Ventas'!A1"/>
+    <hyperlink ref="J1" location="'💸 Gastos'!A1"/>
+    <hyperlink ref="L1" location="'🎯 Objetivos'!A1"/>
+    <hyperlink ref="N1" location="'🔬 Simulador'!A1"/>
+    <hyperlink ref="B6" location="'🏠 Inicio'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/build/Profitly.xlsx
+++ b/build/Profitly.xlsx
@@ -919,7 +919,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_DashboardData'!B21</f>
+              <f>'_DashboardData'!B22</f>
             </strRef>
           </tx>
           <spPr>
@@ -940,12 +940,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_DashboardData'!$A$22:$A$28</f>
+              <f>'_DashboardData'!$A$23:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_DashboardData'!$B$22:$B$28</f>
+              <f>'_DashboardData'!$B$23:$B$28</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -955,7 +955,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'_DashboardData'!C21</f>
+              <f>'_DashboardData'!C22</f>
             </strRef>
           </tx>
           <spPr>
@@ -976,12 +976,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_DashboardData'!$A$22:$A$28</f>
+              <f>'_DashboardData'!$A$23:$A$28</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_DashboardData'!$C$22:$C$28</f>
+              <f>'_DashboardData'!$C$23:$C$28</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1049,7 +1049,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_DashboardData'!B31</f>
+              <f>'_DashboardData'!B32</f>
             </strRef>
           </tx>
           <spPr>
@@ -1062,12 +1062,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'_DashboardData'!$A$32:$A$41</f>
+              <f>'_DashboardData'!$A$33:$A$41</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_DashboardData'!$B$32:$B$41</f>
+              <f>'_DashboardData'!$B$33:$B$41</f>
             </numRef>
           </val>
         </ser>
@@ -1235,7 +1235,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_Demo_Datos'!B126</f>
+              <f>'_Demo_Datos'!B127</f>
             </strRef>
           </tx>
           <spPr>
@@ -1256,12 +1256,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_Demo_Datos'!$A$127:$A$132</f>
+              <f>'_Demo_Datos'!$A$128:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_Demo_Datos'!$B$127:$B$132</f>
+              <f>'_Demo_Datos'!$B$128:$B$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1271,7 +1271,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'_Demo_Datos'!C126</f>
+              <f>'_Demo_Datos'!C127</f>
             </strRef>
           </tx>
           <spPr>
@@ -1292,12 +1292,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_Demo_Datos'!$A$127:$A$132</f>
+              <f>'_Demo_Datos'!$A$128:$A$132</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_Demo_Datos'!$C$127:$C$132</f>
+              <f>'_Demo_Datos'!$C$128:$C$132</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1365,7 +1365,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'_Demo_Datos'!B115</f>
+              <f>'_Demo_Datos'!B116</f>
             </strRef>
           </tx>
           <spPr>
@@ -1378,12 +1378,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'_Demo_Datos'!$A$116:$A$123</f>
+              <f>'_Demo_Datos'!$A$117:$A$123</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_Demo_Datos'!$B$116:$B$123</f>
+              <f>'_Demo_Datos'!$B$117:$B$123</f>
             </numRef>
           </val>
         </ser>
@@ -11163,7 +11163,7 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation sqref="G7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
-      <formula1>=Lst_PeriodosRapidos</formula1>
+      <formula1>Lst_PeriodosRapidos</formula1>
     </dataValidation>
     <dataValidation sqref="F9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="GANANCIA REAL" prompt="Lo que realmente te queda después de descontar los costos de cada venta y los gastos generales de tu negocio."/>
     <dataValidation sqref="J9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="MARGEN" prompt="Porcentaje de tus ventas que queda después de descontar los costos asociados a vender."/>
@@ -11522,7 +11522,7 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lst_Monedas</formula1>
+      <formula1>Lst_Monedas</formula1>
     </dataValidation>
     <dataValidation sqref="C35" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -11853,7 +11853,7 @@
     <dataValidation sqref="F7" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Más vendido" prompt="El producto que más unidades vendiste. No es necesariamente el que más ganancia te deja — mirá &quot;Más rentable&quot; para eso."/>
     <dataValidation sqref="F12" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Comisión %" prompt="Se completa solo cuando elegís un producto — lo podés cambiar."/>
     <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Categoría inválida" error="Elegí una categoría de la lista." type="list">
-      <formula1>=Lst_Categorias</formula1>
+      <formula1>Lst_Categorias</formula1>
     </dataValidation>
     <dataValidation sqref="D13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor inválido" error="Ingresá un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -11878,7 +11878,7 @@
       <formula2>1</formula2>
     </dataValidation>
     <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Nombre duplicado" error="Ya existe un producto con este nombre. Elegí un nombre distinto para diferenciarlo." type="custom">
-      <formula1>=COUNTIF(tbl_Productos[Producto],B13)&lt;=1</formula1>
+      <formula1>COUNTIF(tbl_Productos[Producto],B13)&lt;=1</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
@@ -12110,10 +12110,10 @@
     <dataValidation sqref="E9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Precio de venta" prompt="Ingresá el precio al que vendiste — fijate el precio actual en 📦 Productos si querés usarlo de referencia."/>
     <dataValidation sqref="G9" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Comisión %" prompt="Ingresá la comisión de esta venta — fijate la comisión del producto en 📦 Productos si querés usarla de referencia."/>
     <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Producto inválido" error="Elegí un producto de tu catálogo." type="list">
-      <formula1>=tbl_Productos[Producto]</formula1>
+      <formula1>tbl_Productos[Producto]</formula1>
     </dataValidation>
     <dataValidation sqref="F10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Canal inválido" error="Elegí un canal de la lista." type="list">
-      <formula1>=Lst_Canales</formula1>
+      <formula1>Lst_Canales</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fecha inválida" error="La fecha no puede ser futura." type="date" operator="lessThanOrEqual">
       <formula1>TODAY()</formula1>
@@ -12307,10 +12307,10 @@
   </mergeCells>
   <dataValidations count="4">
     <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lst_CategoriasGasto</formula1>
+      <formula1>Lst_CategoriasGasto</formula1>
     </dataValidation>
     <dataValidation sqref="F10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lst_TiposGasto</formula1>
+      <formula1>Lst_TiposGasto</formula1>
     </dataValidation>
     <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Fecha inválida" error="La fecha no puede ser futura." type="date" operator="lessThanOrEqual">
       <formula1>TODAY()</formula1>
@@ -12555,10 +12555,10 @@
     <dataValidation sqref="F13" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Facturación necesaria" prompt="Cuánto necesitás vender (no ganar) para llegar a tu objetivo, según tu margen actual."/>
     <dataValidation sqref="F14" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="0" promptTitle="Ventas necesarias" prompt="Cuántas ventas necesitás, según tu ticket promedio, para llegar a esa facturación."/>
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Período inválido" error="Elegí el primer día del mes que querés planificar." type="custom">
-      <formula1>=DAY(B7)=1</formula1>
+      <formula1>DAY(B7)=1</formula1>
     </dataValidation>
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Período duplicado" error="Ya definiste un objetivo para este mes — editá la fila existente." type="custom">
-      <formula1>=COUNTIF(tbl_Objetivos[Periodo (Mes-Año)],B7)&lt;=1</formula1>
+      <formula1>COUNTIF(tbl_Objetivos[Periodo (Mes-Año)],B7)&lt;=1</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>

--- a/build/Profitly.xlsx
+++ b/build/Profitly.xlsx
@@ -188,206 +188,206 @@
   </numFmts>
   <fonts count="35">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="10"/>
+      <color rgb="001F2937"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="10"/>
+      <color rgb="001E3A5F"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="10"/>
+      <color rgb="00FFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="9"/>
+      <color rgb="001E3A5F"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="18"/>
+      <color rgb="001E3A5F"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="18"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="10"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="11"/>
+      <color rgb="001E3A5F"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="9.5"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9.5"/>
     </font>
     <font>
+      <sz val="9.5"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
-      <sz val="9.5"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="9"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="9"/>
+      <color rgb="00FFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="001F2937"/>
       <name val="Arial"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="9.5"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9.5"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
     </font>
     <font>
+      <sz val="9.5"/>
+      <color rgb="003B6E9E"/>
       <name val="Arial"/>
-      <color rgb="003B6E9E"/>
-      <sz val="9.5"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="14"/>
+      <color rgb="001E3A5F"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="14"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="11"/>
+      <color rgb="001F2937"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="15"/>
+      <color rgb="001F2937"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="15"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="8.5"/>
+      <color rgb="00B7791F"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00B7791F"/>
-      <sz val="8.5"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="9"/>
+      <color rgb="001F2937"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="9"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="9.5"/>
+      <color rgb="00B7791F"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00B7791F"/>
-      <sz val="9.5"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="9.5"/>
+      <color rgb="001F2937"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="9.5"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="9"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="15"/>
+      <color rgb="001E3A5F"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="15"/>
     </font>
     <font>
+      <sz val="8.5"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <color rgb="006B7280"/>
-      <sz val="8.5"/>
     </font>
     <font>
+      <sz val="8.5"/>
+      <color rgb="001F2937"/>
       <name val="Arial"/>
-      <color rgb="001F2937"/>
-      <sz val="8.5"/>
     </font>
     <font>
+      <sz val="9.5"/>
+      <color rgb="001F2937"/>
       <name val="Arial"/>
-      <color rgb="001F2937"/>
-      <sz val="9.5"/>
     </font>
     <font>
+      <sz val="9.5"/>
+      <color rgb="00B7791F"/>
       <name val="Arial"/>
-      <color rgb="00B7791F"/>
-      <sz val="9.5"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="8.5"/>
+      <color rgb="001E3A5F"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="8.5"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="13"/>
+      <color rgb="001F2937"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001F2937"/>
-      <sz val="13"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="20"/>
+      <color rgb="001E3A5F"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001E3A5F"/>
-      <sz val="20"/>
     </font>
     <font>
+      <i val="1"/>
+      <sz val="11"/>
+      <color rgb="006B7280"/>
       <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b val="1"/>
+      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="11">
@@ -5523,7 +5523,7 @@
     </row>
     <row r="13">
       <c r="Q13" s="70" t="n">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
     </row>
     <row r="14">
       <c r="Q14" s="70" t="n">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -5633,7 +5633,7 @@
     </row>
     <row r="22">
       <c r="B22" s="70" t="n">
-        <v>46187</v>
+        <v>46191</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
     </row>
     <row r="23">
       <c r="B23" s="70" t="n">
-        <v>46187</v>
+        <v>46191</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -5721,7 +5721,7 @@
     </row>
     <row r="24">
       <c r="B24" s="70" t="n">
-        <v>46189</v>
+        <v>46193</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
     </row>
     <row r="25">
       <c r="B25" s="70" t="n">
-        <v>46190</v>
+        <v>46194</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="26">
       <c r="B26" s="70" t="n">
-        <v>46192</v>
+        <v>46196</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="27">
       <c r="B27" s="70" t="n">
-        <v>46193</v>
+        <v>46197</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
     </row>
     <row r="28">
       <c r="B28" s="70" t="n">
-        <v>46193</v>
+        <v>46197</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="29">
       <c r="B29" s="70" t="n">
-        <v>46195</v>
+        <v>46199</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
     </row>
     <row r="30">
       <c r="B30" s="70" t="n">
-        <v>46196</v>
+        <v>46200</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
     </row>
     <row r="31">
       <c r="B31" s="70" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
     </row>
     <row r="32">
       <c r="B32" s="70" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
     </row>
     <row r="33">
       <c r="B33" s="70" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -6161,7 +6161,7 @@
     </row>
     <row r="34">
       <c r="B34" s="70" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
     </row>
     <row r="35">
       <c r="B35" s="70" t="n">
-        <v>46200</v>
+        <v>46204</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -6249,7 +6249,7 @@
     </row>
     <row r="36">
       <c r="B36" s="70" t="n">
-        <v>46200</v>
+        <v>46204</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
     </row>
     <row r="37">
       <c r="B37" s="70" t="n">
-        <v>46200</v>
+        <v>46204</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
     </row>
     <row r="38">
       <c r="B38" s="70" t="n">
-        <v>46201</v>
+        <v>46205</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -6381,7 +6381,7 @@
     </row>
     <row r="39">
       <c r="B39" s="70" t="n">
-        <v>46201</v>
+        <v>46205</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -6425,7 +6425,7 @@
     </row>
     <row r="40">
       <c r="B40" s="70" t="n">
-        <v>46202</v>
+        <v>46206</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
     </row>
     <row r="41">
       <c r="B41" s="70" t="n">
-        <v>46203</v>
+        <v>46207</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -6513,7 +6513,7 @@
     </row>
     <row r="42">
       <c r="B42" s="70" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="43">
       <c r="B43" s="70" t="n">
-        <v>46204</v>
+        <v>46208</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
     </row>
     <row r="44">
       <c r="B44" s="70" t="n">
-        <v>46206</v>
+        <v>46210</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
     </row>
     <row r="45">
       <c r="B45" s="70" t="n">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -6689,7 +6689,7 @@
     </row>
     <row r="46">
       <c r="B46" s="70" t="n">
-        <v>46207</v>
+        <v>46211</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6733,7 +6733,7 @@
     </row>
     <row r="47">
       <c r="B47" s="70" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
     </row>
     <row r="48">
       <c r="B48" s="70" t="n">
-        <v>46208</v>
+        <v>46212</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
     </row>
     <row r="49">
       <c r="B49" s="70" t="n">
-        <v>46210</v>
+        <v>46214</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
     </row>
     <row r="50">
       <c r="B50" s="70" t="n">
-        <v>46211</v>
+        <v>46215</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="51">
       <c r="B51" s="70" t="n">
-        <v>46211</v>
+        <v>46215</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
     </row>
     <row r="52">
       <c r="B52" s="70" t="n">
-        <v>46211</v>
+        <v>46215</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
     </row>
     <row r="53">
       <c r="B53" s="70" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -7041,7 +7041,7 @@
     </row>
     <row r="54">
       <c r="B54" s="70" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
     </row>
     <row r="55">
       <c r="B55" s="70" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
     </row>
     <row r="56">
       <c r="B56" s="70" t="n">
-        <v>46214</v>
+        <v>46218</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
     </row>
     <row r="57">
       <c r="B57" s="70" t="n">
-        <v>46218</v>
+        <v>46222</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="58">
       <c r="B58" s="70" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7261,7 +7261,7 @@
     </row>
     <row r="59">
       <c r="B59" s="70" t="n">
-        <v>46221</v>
+        <v>46225</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
     </row>
     <row r="60">
       <c r="B60" s="70" t="n">
-        <v>46221</v>
+        <v>46225</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7349,7 +7349,7 @@
     </row>
     <row r="61">
       <c r="B61" s="70" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
     </row>
     <row r="62">
       <c r="B62" s="70" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
     </row>
     <row r="63">
       <c r="B63" s="70" t="n">
-        <v>46225</v>
+        <v>46229</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="64">
       <c r="B64" s="70" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7525,7 +7525,7 @@
     </row>
     <row r="65">
       <c r="B65" s="70" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7569,7 +7569,7 @@
     </row>
     <row r="66">
       <c r="B66" s="70" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
     </row>
     <row r="67">
       <c r="B67" s="70" t="n">
-        <v>46228</v>
+        <v>46232</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7657,7 +7657,7 @@
     </row>
     <row r="68">
       <c r="B68" s="70" t="n">
-        <v>46231</v>
+        <v>46235</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7701,7 +7701,7 @@
     </row>
     <row r="69">
       <c r="B69" s="70" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
     </row>
     <row r="70">
       <c r="B70" s="70" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7789,7 +7789,7 @@
     </row>
     <row r="71">
       <c r="B71" s="70" t="n">
-        <v>46232</v>
+        <v>46236</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7833,7 +7833,7 @@
     </row>
     <row r="72">
       <c r="B72" s="70" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -7877,7 +7877,7 @@
     </row>
     <row r="73">
       <c r="B73" s="70" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
     </row>
     <row r="74">
       <c r="B74" s="70" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -7965,7 +7965,7 @@
     </row>
     <row r="75">
       <c r="B75" s="70" t="n">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8009,7 +8009,7 @@
     </row>
     <row r="76">
       <c r="B76" s="70" t="n">
-        <v>46235</v>
+        <v>46239</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8053,7 +8053,7 @@
     </row>
     <row r="77">
       <c r="B77" s="70" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
     </row>
     <row r="78">
       <c r="B78" s="70" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8141,7 +8141,7 @@
     </row>
     <row r="79">
       <c r="B79" s="70" t="n">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
     </row>
     <row r="80">
       <c r="B80" s="70" t="n">
-        <v>46238</v>
+        <v>46242</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8229,7 +8229,7 @@
     </row>
     <row r="81">
       <c r="B81" s="70" t="n">
-        <v>46239</v>
+        <v>46243</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
     </row>
     <row r="82">
       <c r="B82" s="70" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
     </row>
     <row r="83">
       <c r="B83" s="70" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -8361,7 +8361,7 @@
     </row>
     <row r="84">
       <c r="B84" s="70" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -8405,7 +8405,7 @@
     </row>
     <row r="85">
       <c r="B85" s="70" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -8449,7 +8449,7 @@
     </row>
     <row r="86">
       <c r="B86" s="70" t="n">
-        <v>46242</v>
+        <v>46246</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
     </row>
     <row r="87">
       <c r="B87" s="70" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -8537,7 +8537,7 @@
     </row>
     <row r="88">
       <c r="B88" s="70" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
     </row>
     <row r="89">
       <c r="B89" s="70" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -8625,7 +8625,7 @@
     </row>
     <row r="90">
       <c r="B90" s="70" t="n">
-        <v>46244</v>
+        <v>46248</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
     </row>
     <row r="91">
       <c r="B91" s="70" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -8713,7 +8713,7 @@
     </row>
     <row r="92">
       <c r="B92" s="70" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
     </row>
     <row r="93">
       <c r="B93" s="70" t="n">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -8801,7 +8801,7 @@
     </row>
     <row r="94">
       <c r="B94" s="70" t="n">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
     </row>
     <row r="95">
       <c r="B95" s="70" t="n">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
     </row>
     <row r="96">
       <c r="B96" s="70" t="n">
-        <v>46246</v>
+        <v>46250</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
     </row>
     <row r="97">
       <c r="B97" s="70" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -8977,7 +8977,7 @@
     </row>
     <row r="98">
       <c r="B98" s="70" t="n">
-        <v>46249</v>
+        <v>46253</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
     </row>
     <row r="99">
       <c r="B99" s="70" t="n">
-        <v>46250</v>
+        <v>46254</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
     </row>
     <row r="100">
       <c r="B100" s="70" t="n">
-        <v>46252</v>
+        <v>46256</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
     </row>
     <row r="101">
       <c r="B101" s="70" t="n">
-        <v>46252</v>
+        <v>46256</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
     </row>
     <row r="102">
       <c r="B102" s="70" t="n">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
     </row>
     <row r="103">
       <c r="B103" s="70" t="n">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
     </row>
     <row r="104">
       <c r="B104" s="70" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
     </row>
     <row r="105">
       <c r="B105" s="70" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
     </row>
     <row r="106">
       <c r="B106" s="70" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="107">
       <c r="B107" s="70" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
     </row>
     <row r="108">
       <c r="B108" s="70" t="n">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
     </row>
     <row r="109">
       <c r="B109" s="70" t="n">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -9505,7 +9505,7 @@
     </row>
     <row r="110">
       <c r="B110" s="70" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -9549,7 +9549,7 @@
     </row>
     <row r="111">
       <c r="B111" s="70" t="n">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -9593,7 +9593,7 @@
     </row>
     <row r="112">
       <c r="B112" s="70" t="n">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -9637,7 +9637,7 @@
     </row>
     <row r="113">
       <c r="B113" s="70" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -9681,7 +9681,7 @@
     </row>
     <row r="114">
       <c r="B114" s="70" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="B115" s="70" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -10166,7 +10166,7 @@
     </row>
     <row r="124">
       <c r="B124" s="70" t="n">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
     </row>
     <row r="125">
       <c r="B125" s="70" t="n">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         </is>
       </c>
       <c r="B126" s="70" t="n">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
